--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8146,6 +8146,122 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122879089</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80434</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>738</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Gyalecta ulmi</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bennestad, Almskog, Sk</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>432213</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6152973</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Skogslönn</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Skogslönn</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Gärdsborn</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Gärdsborn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8262,6 +8262,3080 @@
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123312991</v>
+      </c>
+      <c r="B62" t="n">
+        <v>94865</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>432217</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6152972</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123313165</v>
+      </c>
+      <c r="B63" t="n">
+        <v>94659</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>432332</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6152958</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123313167</v>
+      </c>
+      <c r="B64" t="n">
+        <v>74759</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Stiftklotterlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Opegrapha vermicellifera</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Kunze) J.R.Laundon</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>432332</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6152958</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123313208</v>
+      </c>
+      <c r="B65" t="n">
+        <v>74764</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1458</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grå skärelav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dendrographa decolorans</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>432329</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6152963</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>123313000</v>
+      </c>
+      <c r="B66" t="n">
+        <v>94869</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>432217</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6152972</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123313105</v>
+      </c>
+      <c r="B67" t="n">
+        <v>94659</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>432268</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6152997</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>123313420</v>
+      </c>
+      <c r="B68" t="n">
+        <v>74759</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Stiftklotterlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Opegrapha vermicellifera</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Kunze) J.R.Laundon</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>432198</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6152961</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>123313446</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79146</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>432147</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6152962</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123313433</v>
+      </c>
+      <c r="B70" t="n">
+        <v>74759</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Stiftklotterlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Opegrapha vermicellifera</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Kunze) J.R.Laundon</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>432147</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6152962</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>123313425</v>
+      </c>
+      <c r="B71" t="n">
+        <v>94865</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>432198</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6152961</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>123313109</v>
+      </c>
+      <c r="B72" t="n">
+        <v>94614</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>432268</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6152997</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>123312996</v>
+      </c>
+      <c r="B73" t="n">
+        <v>94614</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>432217</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6152972</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>123313362</v>
+      </c>
+      <c r="B74" t="n">
+        <v>74759</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Stiftklotterlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Opegrapha vermicellifera</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Kunze) J.R.Laundon</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>432240</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6153018</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>123313365</v>
+      </c>
+      <c r="B75" t="n">
+        <v>94659</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>432240</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6153018</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123313438</v>
+      </c>
+      <c r="B76" t="n">
+        <v>74847</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>432147</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6152962</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123313384</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80434</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>738</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Gyalecta ulmi</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>432198</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6152961</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>123313092</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80434</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>738</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Gyalecta ulmi</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>432268</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6152997</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123313163</v>
+      </c>
+      <c r="B79" t="n">
+        <v>77102</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>432332</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6152958</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>123313422</v>
+      </c>
+      <c r="B80" t="n">
+        <v>94659</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>432198</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6152961</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>123312986</v>
+      </c>
+      <c r="B81" t="n">
+        <v>94659</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>432217</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6152972</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>123313107</v>
+      </c>
+      <c r="B82" t="n">
+        <v>94865</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>432268</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6152997</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>123313155</v>
+      </c>
+      <c r="B83" t="n">
+        <v>110138</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>432332</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6152958</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>123313426</v>
+      </c>
+      <c r="B84" t="n">
+        <v>94869</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>432198</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6152961</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>123312983</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80434</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>738</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Gyalecta ulmi</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>432217</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6152972</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>123313436</v>
+      </c>
+      <c r="B86" t="n">
+        <v>94659</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>432147</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6152962</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -9606,10 +9606,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123312996</v>
+        <v>123313362</v>
       </c>
       <c r="B73" t="n">
-        <v>94614</v>
+        <v>74759</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9618,31 +9618,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2676</v>
+        <v>1118</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9650,10 +9649,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432217</v>
+        <v>432240</v>
       </c>
       <c r="R73" t="n">
-        <v>6152972</v>
+        <v>6153018</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9690,7 +9689,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Gammal avenbok</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9705,17 +9704,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9733,10 +9732,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313362</v>
+        <v>123313365</v>
       </c>
       <c r="B74" t="n">
-        <v>74759</v>
+        <v>94659</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9745,30 +9744,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9812,11 +9812,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9859,10 +9854,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313365</v>
+        <v>123313438</v>
       </c>
       <c r="B75" t="n">
-        <v>94659</v>
+        <v>74847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9875,27 +9870,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2779</v>
+        <v>6439</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9903,10 +9897,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432240</v>
+        <v>432147</v>
       </c>
       <c r="R75" t="n">
-        <v>6153018</v>
+        <v>6152962</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9953,17 +9947,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9981,10 +9975,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313438</v>
+        <v>123313384</v>
       </c>
       <c r="B76" t="n">
-        <v>74847</v>
+        <v>80434</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9993,29 +9987,37 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6439</v>
+        <v>738</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -10024,10 +10026,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R76" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10102,7 +10104,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313384</v>
+        <v>123313092</v>
       </c>
       <c r="B77" t="n">
         <v>80434</v>
@@ -10137,7 +10139,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10153,10 +10155,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432198</v>
+        <v>432268</v>
       </c>
       <c r="R77" t="n">
-        <v>6152961</v>
+        <v>6152997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10189,6 +10191,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10231,10 +10238,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313092</v>
+        <v>123313163</v>
       </c>
       <c r="B78" t="n">
-        <v>80434</v>
+        <v>77102</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10243,37 +10250,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>738</v>
+        <v>1342</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -10282,10 +10281,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432268</v>
+        <v>432332</v>
       </c>
       <c r="R78" t="n">
-        <v>6152997</v>
+        <v>6152958</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10322,7 +10321,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Liten förekomst i dåligt skick.</t>
+          <t>Rikligt på gammal avenbok</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10337,17 +10336,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10365,10 +10364,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313163</v>
+        <v>123313422</v>
       </c>
       <c r="B79" t="n">
-        <v>77102</v>
+        <v>94659</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10377,30 +10376,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R79" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10446,11 +10446,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10463,17 +10458,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10491,7 +10486,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313422</v>
+        <v>123312986</v>
       </c>
       <c r="B80" t="n">
         <v>94659</v>
@@ -10535,10 +10530,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R80" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10613,10 +10608,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123312986</v>
+        <v>123313107</v>
       </c>
       <c r="B81" t="n">
-        <v>94659</v>
+        <v>94865</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10629,21 +10624,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10657,10 +10652,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R81" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10735,10 +10730,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313107</v>
+        <v>123313155</v>
       </c>
       <c r="B82" t="n">
-        <v>94865</v>
+        <v>110138</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10747,30 +10742,34 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2667</v>
+        <v>222776</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -10779,10 +10778,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432268</v>
+        <v>432332</v>
       </c>
       <c r="R82" t="n">
-        <v>6152997</v>
+        <v>6152958</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10826,21 +10825,6 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10857,10 +10841,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313155</v>
+        <v>123313426</v>
       </c>
       <c r="B83" t="n">
-        <v>110138</v>
+        <v>94869</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10869,34 +10853,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222776</v>
+        <v>2668</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -10905,10 +10885,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R83" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10952,6 +10932,21 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10968,10 +10963,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313426</v>
+        <v>123312983</v>
       </c>
       <c r="B84" t="n">
-        <v>94869</v>
+        <v>80434</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10980,31 +10975,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2668</v>
+        <v>738</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11012,10 +11006,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R84" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11048,6 +11042,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11090,10 +11089,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123312983</v>
+        <v>123313436</v>
       </c>
       <c r="B85" t="n">
-        <v>80434</v>
+        <v>94659</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11102,30 +11101,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432217</v>
+        <v>432147</v>
       </c>
       <c r="R85" t="n">
-        <v>6152972</v>
+        <v>6152962</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11169,11 +11169,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11216,14 +11211,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123313436</v>
+        <v>123312996</v>
       </c>
       <c r="B86" t="n">
-        <v>94659</v>
+        <v>94614</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11232,21 +11227,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11260,10 +11255,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>432147</v>
+        <v>432217</v>
       </c>
       <c r="R86" t="n">
-        <v>6152962</v>
+        <v>6152972</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11296,6 +11291,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8151,7 +8151,7 @@
         <v>122879089</v>
       </c>
       <c r="B61" t="n">
-        <v>80434</v>
+        <v>80437</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>123312991</v>
       </c>
       <c r="B62" t="n">
-        <v>94865</v>
+        <v>94868</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313165</v>
+        <v>123313426</v>
       </c>
       <c r="B63" t="n">
-        <v>94659</v>
+        <v>94872</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8402,21 +8402,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8430,10 +8430,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R63" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8480,17 +8480,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
         <v>123313167</v>
       </c>
       <c r="B64" t="n">
-        <v>74759</v>
+        <v>74762</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313208</v>
+        <v>123312983</v>
       </c>
       <c r="B65" t="n">
-        <v>74764</v>
+        <v>80437</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8641,25 +8641,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1458</v>
+        <v>738</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8672,10 +8672,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432329</v>
+        <v>432217</v>
       </c>
       <c r="R65" t="n">
-        <v>6152963</v>
+        <v>6152972</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8710,6 +8710,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8722,17 +8727,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8750,10 +8755,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313000</v>
+        <v>123312986</v>
       </c>
       <c r="B66" t="n">
-        <v>94869</v>
+        <v>94662</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8766,21 +8771,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8832,11 +8837,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8877,10 +8877,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313105</v>
+        <v>123313165</v>
       </c>
       <c r="B67" t="n">
-        <v>94659</v>
+        <v>94662</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432268</v>
+        <v>432332</v>
       </c>
       <c r="R67" t="n">
-        <v>6152997</v>
+        <v>6152958</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313420</v>
+        <v>123313446</v>
       </c>
       <c r="B68" t="n">
-        <v>74759</v>
+        <v>79149</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9011,25 +9011,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1118</v>
+        <v>6431</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R68" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9120,10 +9120,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313446</v>
+        <v>123313420</v>
       </c>
       <c r="B69" t="n">
-        <v>79146</v>
+        <v>74762</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9132,25 +9132,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6431</v>
+        <v>1118</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R69" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9241,10 +9241,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123313433</v>
+        <v>123313362</v>
       </c>
       <c r="B70" t="n">
-        <v>74759</v>
+        <v>74762</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9284,10 +9284,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432147</v>
+        <v>432240</v>
       </c>
       <c r="R70" t="n">
-        <v>6152962</v>
+        <v>6153018</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9322,6 +9322,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9334,17 +9339,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9362,10 +9367,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313425</v>
+        <v>123313433</v>
       </c>
       <c r="B71" t="n">
-        <v>94865</v>
+        <v>74762</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9374,31 +9379,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2667</v>
+        <v>1118</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9406,10 +9410,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R71" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9484,10 +9488,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313109</v>
+        <v>123313425</v>
       </c>
       <c r="B72" t="n">
-        <v>94614</v>
+        <v>94868</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9500,21 +9504,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2676</v>
+        <v>2667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9528,10 +9532,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R72" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9606,10 +9610,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313362</v>
+        <v>123313155</v>
       </c>
       <c r="B73" t="n">
-        <v>74759</v>
+        <v>110144</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9622,26 +9626,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1118</v>
+        <v>222776</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9649,10 +9658,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432240</v>
+        <v>432332</v>
       </c>
       <c r="R73" t="n">
-        <v>6153018</v>
+        <v>6152958</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9687,11 +9696,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9701,21 +9705,6 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>avenbok</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Carpinus betulus</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Carpinus betulus</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9732,10 +9721,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313365</v>
+        <v>123313107</v>
       </c>
       <c r="B74" t="n">
-        <v>94659</v>
+        <v>94868</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9748,21 +9737,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9776,10 +9765,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432240</v>
+        <v>432268</v>
       </c>
       <c r="R74" t="n">
-        <v>6153018</v>
+        <v>6152997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9826,17 +9815,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9854,10 +9843,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313438</v>
+        <v>123313109</v>
       </c>
       <c r="B75" t="n">
-        <v>74847</v>
+        <v>94617</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9870,26 +9859,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6439</v>
+        <v>2676</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9897,10 +9887,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432147</v>
+        <v>432268</v>
       </c>
       <c r="R75" t="n">
-        <v>6152962</v>
+        <v>6152997</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9975,10 +9965,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313384</v>
+        <v>123313163</v>
       </c>
       <c r="B76" t="n">
-        <v>80434</v>
+        <v>77105</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9987,37 +9977,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>738</v>
+        <v>1342</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -10026,10 +10008,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432198</v>
+        <v>432332</v>
       </c>
       <c r="R76" t="n">
-        <v>6152961</v>
+        <v>6152958</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10064,6 +10046,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10076,17 +10063,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10104,10 +10091,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313092</v>
+        <v>123313436</v>
       </c>
       <c r="B77" t="n">
-        <v>80434</v>
+        <v>94662</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10116,38 +10103,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10155,10 +10135,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432268</v>
+        <v>432147</v>
       </c>
       <c r="R77" t="n">
-        <v>6152997</v>
+        <v>6152962</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10191,11 +10171,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10238,10 +10213,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313163</v>
+        <v>123313384</v>
       </c>
       <c r="B78" t="n">
-        <v>77102</v>
+        <v>80437</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10250,29 +10225,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1342</v>
+        <v>738</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -10281,10 +10264,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R78" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10319,11 +10302,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10336,17 +10314,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10364,10 +10342,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313422</v>
+        <v>123313000</v>
       </c>
       <c r="B79" t="n">
-        <v>94659</v>
+        <v>94872</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10380,21 +10358,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10408,10 +10386,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R79" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10444,6 +10422,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10486,10 +10469,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123312986</v>
+        <v>123313092</v>
       </c>
       <c r="B80" t="n">
-        <v>94659</v>
+        <v>80437</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10498,31 +10481,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10530,10 +10520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R80" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10566,6 +10556,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10608,10 +10603,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313107</v>
+        <v>123313105</v>
       </c>
       <c r="B81" t="n">
-        <v>94865</v>
+        <v>94662</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10624,21 +10619,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10730,10 +10725,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313155</v>
+        <v>123313438</v>
       </c>
       <c r="B82" t="n">
-        <v>110138</v>
+        <v>74850</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10742,35 +10737,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222776</v>
+        <v>6439</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10778,10 +10768,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R82" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10825,6 +10815,21 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10841,10 +10846,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313426</v>
+        <v>123313422</v>
       </c>
       <c r="B83" t="n">
-        <v>94869</v>
+        <v>94662</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10857,21 +10862,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10963,10 +10968,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123312983</v>
+        <v>123313365</v>
       </c>
       <c r="B84" t="n">
-        <v>80434</v>
+        <v>94662</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10975,30 +10980,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11006,10 +11012,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432217</v>
+        <v>432240</v>
       </c>
       <c r="R84" t="n">
-        <v>6152972</v>
+        <v>6153018</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11044,11 +11050,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11061,17 +11062,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11089,10 +11090,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123313436</v>
+        <v>123313208</v>
       </c>
       <c r="B85" t="n">
-        <v>94659</v>
+        <v>74767</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11105,27 +11106,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2779</v>
+        <v>1458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432147</v>
+        <v>432329</v>
       </c>
       <c r="R85" t="n">
-        <v>6152962</v>
+        <v>6152963</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11183,17 +11183,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
         <v>123312996</v>
       </c>
       <c r="B86" t="n">
-        <v>94614</v>
+        <v>94617</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8151,7 +8151,7 @@
         <v>122879089</v>
       </c>
       <c r="B61" t="n">
-        <v>80437</v>
+        <v>80439</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123312991</v>
+        <v>123313155</v>
       </c>
       <c r="B62" t="n">
-        <v>94868</v>
+        <v>110146</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8276,30 +8276,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2667</v>
+        <v>222776</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -8308,10 +8312,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R62" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8355,21 +8359,6 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8386,10 +8375,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313426</v>
+        <v>123313420</v>
       </c>
       <c r="B63" t="n">
-        <v>94872</v>
+        <v>74762</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8398,31 +8387,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2668</v>
+        <v>1118</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8508,10 +8496,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313167</v>
+        <v>123313436</v>
       </c>
       <c r="B64" t="n">
-        <v>74762</v>
+        <v>94664</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8520,30 +8508,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8551,10 +8540,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R64" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8601,17 +8590,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8629,10 +8618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123312983</v>
+        <v>123313092</v>
       </c>
       <c r="B65" t="n">
-        <v>80437</v>
+        <v>80439</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8662,8 +8651,16 @@
           <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -8672,10 +8669,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R65" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8712,7 +8709,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8755,10 +8752,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123312986</v>
+        <v>123313438</v>
       </c>
       <c r="B66" t="n">
-        <v>94662</v>
+        <v>74850</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8771,27 +8768,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2779</v>
+        <v>6439</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8799,10 +8795,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432217</v>
+        <v>432147</v>
       </c>
       <c r="R66" t="n">
-        <v>6152972</v>
+        <v>6152962</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8877,10 +8873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313165</v>
+        <v>123313105</v>
       </c>
       <c r="B67" t="n">
-        <v>94662</v>
+        <v>94664</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8921,10 +8917,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R67" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8971,17 +8967,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8999,10 +8995,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313446</v>
+        <v>123313384</v>
       </c>
       <c r="B68" t="n">
-        <v>79149</v>
+        <v>80439</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9011,29 +9007,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6431</v>
+        <v>738</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -9042,10 +9046,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R68" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9120,10 +9124,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313420</v>
+        <v>123313422</v>
       </c>
       <c r="B69" t="n">
-        <v>74762</v>
+        <v>94664</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9132,30 +9136,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9241,7 +9246,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123313362</v>
+        <v>123313433</v>
       </c>
       <c r="B70" t="n">
         <v>74762</v>
@@ -9284,10 +9289,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432240</v>
+        <v>432147</v>
       </c>
       <c r="R70" t="n">
-        <v>6153018</v>
+        <v>6152962</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9322,11 +9327,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9339,17 +9339,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9367,7 +9367,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313433</v>
+        <v>123313362</v>
       </c>
       <c r="B71" t="n">
         <v>74762</v>
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432147</v>
+        <v>432240</v>
       </c>
       <c r="R71" t="n">
-        <v>6152962</v>
+        <v>6153018</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9448,6 +9448,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9460,17 +9465,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9488,10 +9493,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313425</v>
+        <v>123313426</v>
       </c>
       <c r="B72" t="n">
-        <v>94868</v>
+        <v>94874</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9504,21 +9509,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9610,10 +9615,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313155</v>
+        <v>123313425</v>
       </c>
       <c r="B73" t="n">
-        <v>110144</v>
+        <v>94870</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9622,34 +9627,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222776</v>
+        <v>2667</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9658,10 +9659,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R73" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9705,6 +9706,21 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9721,10 +9737,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313107</v>
+        <v>123312991</v>
       </c>
       <c r="B74" t="n">
-        <v>94868</v>
+        <v>94870</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9765,10 +9781,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R74" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9843,10 +9859,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313109</v>
+        <v>123313165</v>
       </c>
       <c r="B75" t="n">
-        <v>94617</v>
+        <v>94664</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9859,21 +9875,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2676</v>
+        <v>2779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9887,10 +9903,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432268</v>
+        <v>432332</v>
       </c>
       <c r="R75" t="n">
-        <v>6152997</v>
+        <v>6152958</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9937,17 +9953,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9965,10 +9981,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313163</v>
+        <v>123312983</v>
       </c>
       <c r="B76" t="n">
-        <v>77105</v>
+        <v>80439</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9977,25 +9993,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1342</v>
+        <v>738</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10008,10 +10024,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432332</v>
+        <v>432217</v>
       </c>
       <c r="R76" t="n">
-        <v>6152958</v>
+        <v>6152972</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10048,7 +10064,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt på gammal avenbok</t>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10063,17 +10079,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10091,10 +10107,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313436</v>
+        <v>123313163</v>
       </c>
       <c r="B77" t="n">
-        <v>94662</v>
+        <v>77107</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10103,31 +10119,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10135,10 +10150,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R77" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10173,6 +10188,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10185,17 +10205,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10213,10 +10233,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313384</v>
+        <v>123313365</v>
       </c>
       <c r="B78" t="n">
-        <v>80437</v>
+        <v>94664</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10225,38 +10245,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10264,10 +10277,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432198</v>
+        <v>432240</v>
       </c>
       <c r="R78" t="n">
-        <v>6152961</v>
+        <v>6153018</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10314,17 +10327,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10342,10 +10355,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313000</v>
+        <v>123313109</v>
       </c>
       <c r="B79" t="n">
-        <v>94872</v>
+        <v>94619</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10358,21 +10371,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2668</v>
+        <v>2676</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10386,10 +10399,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R79" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10422,11 +10435,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10469,10 +10477,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313092</v>
+        <v>123313107</v>
       </c>
       <c r="B80" t="n">
-        <v>80437</v>
+        <v>94870</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10481,38 +10489,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10556,11 +10557,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10603,10 +10599,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313105</v>
+        <v>123313446</v>
       </c>
       <c r="B81" t="n">
-        <v>94662</v>
+        <v>79151</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10619,27 +10615,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10647,10 +10642,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432268</v>
+        <v>432147</v>
       </c>
       <c r="R81" t="n">
-        <v>6152997</v>
+        <v>6152962</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10725,10 +10720,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313438</v>
+        <v>123313167</v>
       </c>
       <c r="B82" t="n">
-        <v>74850</v>
+        <v>74762</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,25 +10732,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6439</v>
+        <v>1118</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10768,10 +10763,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R82" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10818,17 +10813,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10846,10 +10841,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313422</v>
+        <v>123312986</v>
       </c>
       <c r="B83" t="n">
-        <v>94662</v>
+        <v>94664</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10890,10 +10885,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R83" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10968,10 +10963,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313365</v>
+        <v>123313000</v>
       </c>
       <c r="B84" t="n">
-        <v>94662</v>
+        <v>94874</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10984,21 +10979,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432240</v>
+        <v>432217</v>
       </c>
       <c r="R84" t="n">
-        <v>6153018</v>
+        <v>6152972</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11050,6 +11045,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11062,17 +11062,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
         <v>123312996</v>
       </c>
       <c r="B86" t="n">
-        <v>94617</v>
+        <v>94619</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8264,10 +8264,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313155</v>
+        <v>123313420</v>
       </c>
       <c r="B62" t="n">
-        <v>110146</v>
+        <v>74762</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8280,31 +8280,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222776</v>
+        <v>1118</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8312,10 +8307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R62" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8359,6 +8354,21 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8375,10 +8385,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313420</v>
+        <v>123313092</v>
       </c>
       <c r="B63" t="n">
-        <v>74762</v>
+        <v>80439</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8387,29 +8397,37 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -8418,10 +8436,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432198</v>
+        <v>432268</v>
       </c>
       <c r="R63" t="n">
-        <v>6152961</v>
+        <v>6152997</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8454,6 +8472,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8496,10 +8519,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313436</v>
+        <v>123313438</v>
       </c>
       <c r="B64" t="n">
-        <v>94664</v>
+        <v>74850</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8512,27 +8535,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2779</v>
+        <v>6439</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8618,10 +8640,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313092</v>
+        <v>123313436</v>
       </c>
       <c r="B65" t="n">
-        <v>80439</v>
+        <v>94664</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8630,38 +8652,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8669,10 +8684,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432268</v>
+        <v>432147</v>
       </c>
       <c r="R65" t="n">
-        <v>6152997</v>
+        <v>6152962</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8705,11 +8720,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8752,10 +8762,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313438</v>
+        <v>123313155</v>
       </c>
       <c r="B66" t="n">
-        <v>74850</v>
+        <v>110146</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8764,30 +8774,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6439</v>
+        <v>222776</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8795,10 +8810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R66" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8842,21 +8857,6 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8151,7 +8151,7 @@
         <v>122879089</v>
       </c>
       <c r="B61" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313420</v>
+        <v>123313433</v>
       </c>
       <c r="B62" t="n">
         <v>74762</v>
@@ -8307,10 +8307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R62" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8388,7 +8388,7 @@
         <v>123313092</v>
       </c>
       <c r="B63" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8519,10 +8519,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313438</v>
+        <v>123313420</v>
       </c>
       <c r="B64" t="n">
-        <v>74850</v>
+        <v>74762</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6439</v>
+        <v>1118</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8562,10 +8562,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R64" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313436</v>
+        <v>123313422</v>
       </c>
       <c r="B65" t="n">
-        <v>94664</v>
+        <v>94670</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8684,10 +8684,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R65" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8762,10 +8762,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313155</v>
+        <v>123313107</v>
       </c>
       <c r="B66" t="n">
-        <v>110146</v>
+        <v>94876</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8774,34 +8774,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222776</v>
+        <v>2667</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -8810,10 +8806,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R66" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8857,6 +8853,21 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8873,10 +8884,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313105</v>
+        <v>123313000</v>
       </c>
       <c r="B67" t="n">
-        <v>94664</v>
+        <v>94880</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8889,21 +8900,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8917,10 +8928,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R67" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8953,6 +8964,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8995,10 +9011,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313384</v>
+        <v>123313165</v>
       </c>
       <c r="B68" t="n">
-        <v>80439</v>
+        <v>94670</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9007,38 +9023,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9046,10 +9055,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432198</v>
+        <v>432332</v>
       </c>
       <c r="R68" t="n">
-        <v>6152961</v>
+        <v>6152958</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9096,17 +9105,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9124,10 +9133,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313422</v>
+        <v>123313438</v>
       </c>
       <c r="B69" t="n">
-        <v>94664</v>
+        <v>74850</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9140,27 +9149,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2779</v>
+        <v>6439</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9168,10 +9176,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R69" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9246,7 +9254,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123313433</v>
+        <v>123313362</v>
       </c>
       <c r="B70" t="n">
         <v>74762</v>
@@ -9289,10 +9297,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432147</v>
+        <v>432240</v>
       </c>
       <c r="R70" t="n">
-        <v>6152962</v>
+        <v>6153018</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9327,6 +9335,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9339,17 +9352,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9367,10 +9380,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313362</v>
+        <v>123312991</v>
       </c>
       <c r="B71" t="n">
-        <v>74762</v>
+        <v>94876</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9379,30 +9392,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9410,10 +9424,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432240</v>
+        <v>432217</v>
       </c>
       <c r="R71" t="n">
-        <v>6153018</v>
+        <v>6152972</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9448,11 +9462,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9465,17 +9474,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9493,10 +9502,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313426</v>
+        <v>123313425</v>
       </c>
       <c r="B72" t="n">
-        <v>94874</v>
+        <v>94876</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9509,21 +9518,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9615,10 +9624,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313425</v>
+        <v>123313365</v>
       </c>
       <c r="B73" t="n">
-        <v>94870</v>
+        <v>94670</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9631,21 +9640,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9659,10 +9668,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432198</v>
+        <v>432240</v>
       </c>
       <c r="R73" t="n">
-        <v>6152961</v>
+        <v>6153018</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9709,17 +9718,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9737,10 +9746,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123312991</v>
+        <v>123313155</v>
       </c>
       <c r="B74" t="n">
-        <v>94870</v>
+        <v>110153</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9749,30 +9758,34 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>222776</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -9781,10 +9794,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R74" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9828,21 +9841,6 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9859,10 +9857,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313165</v>
+        <v>123313109</v>
       </c>
       <c r="B75" t="n">
-        <v>94664</v>
+        <v>94625</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9875,21 +9873,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9903,10 +9901,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R75" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9953,17 +9951,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9981,10 +9979,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123312983</v>
+        <v>123313426</v>
       </c>
       <c r="B76" t="n">
-        <v>80439</v>
+        <v>94880</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9993,30 +9991,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>738</v>
+        <v>2668</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10024,10 +10023,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432217</v>
+        <v>432198</v>
       </c>
       <c r="R76" t="n">
-        <v>6152972</v>
+        <v>6152961</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10060,11 +10059,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10107,10 +10101,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313163</v>
+        <v>123313446</v>
       </c>
       <c r="B77" t="n">
-        <v>77107</v>
+        <v>79152</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10119,25 +10113,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1342</v>
+        <v>6431</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10150,10 +10144,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R77" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10188,11 +10182,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10205,17 +10194,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10233,10 +10222,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313365</v>
+        <v>123313384</v>
       </c>
       <c r="B78" t="n">
-        <v>94664</v>
+        <v>80440</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10245,31 +10234,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10277,10 +10273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432240</v>
+        <v>432198</v>
       </c>
       <c r="R78" t="n">
-        <v>6153018</v>
+        <v>6152961</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10327,17 +10323,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10355,10 +10351,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313109</v>
+        <v>123313105</v>
       </c>
       <c r="B79" t="n">
-        <v>94619</v>
+        <v>94670</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10371,21 +10367,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2676</v>
+        <v>2779</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10477,10 +10473,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313107</v>
+        <v>123313163</v>
       </c>
       <c r="B80" t="n">
-        <v>94870</v>
+        <v>77108</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10489,31 +10485,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10521,10 +10516,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432268</v>
+        <v>432332</v>
       </c>
       <c r="R80" t="n">
-        <v>6152997</v>
+        <v>6152958</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10559,6 +10554,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10571,17 +10571,17 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10599,10 +10599,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313446</v>
+        <v>123313167</v>
       </c>
       <c r="B81" t="n">
-        <v>79151</v>
+        <v>74762</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10611,25 +10611,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6431</v>
+        <v>1118</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10642,10 +10642,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R81" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10692,17 +10692,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313167</v>
+        <v>123313436</v>
       </c>
       <c r="B82" t="n">
-        <v>74762</v>
+        <v>94670</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10732,30 +10732,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10763,10 +10764,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R82" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10813,17 +10814,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10841,10 +10842,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123312986</v>
+        <v>123312983</v>
       </c>
       <c r="B83" t="n">
-        <v>94664</v>
+        <v>80440</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10853,31 +10854,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10921,6 +10921,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10963,10 +10968,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313000</v>
+        <v>123312986</v>
       </c>
       <c r="B84" t="n">
-        <v>94874</v>
+        <v>94670</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10979,21 +10984,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11045,11 +11050,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>123312996</v>
       </c>
       <c r="B86" t="n">
-        <v>94619</v>
+        <v>94625</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8264,10 +8264,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313167</v>
+        <v>123313165</v>
       </c>
       <c r="B62" t="n">
-        <v>74765</v>
+        <v>94690</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8276,30 +8276,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8385,10 +8386,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313436</v>
+        <v>123313167</v>
       </c>
       <c r="B63" t="n">
-        <v>94673</v>
+        <v>74771</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8397,31 +8398,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2779</v>
+        <v>1118</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R63" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8479,17 +8479,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8510,7 +8510,7 @@
         <v>123313384</v>
       </c>
       <c r="B64" t="n">
-        <v>80443</v>
+        <v>80449</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123312986</v>
+        <v>123313109</v>
       </c>
       <c r="B65" t="n">
-        <v>94673</v>
+        <v>94645</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8652,21 +8652,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R65" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8758,10 +8758,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313420</v>
+        <v>123312983</v>
       </c>
       <c r="B66" t="n">
-        <v>74765</v>
+        <v>80449</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8770,25 +8770,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R66" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8837,6 +8837,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8879,10 +8884,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313425</v>
+        <v>123312991</v>
       </c>
       <c r="B67" t="n">
-        <v>94879</v>
+        <v>94896</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8923,10 +8928,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R67" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9001,10 +9006,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313422</v>
+        <v>123313163</v>
       </c>
       <c r="B68" t="n">
-        <v>94673</v>
+        <v>77117</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9013,31 +9018,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9045,10 +9049,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432198</v>
+        <v>432332</v>
       </c>
       <c r="R68" t="n">
-        <v>6152961</v>
+        <v>6152958</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9083,6 +9087,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9095,17 +9104,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9123,10 +9132,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313433</v>
+        <v>123313436</v>
       </c>
       <c r="B69" t="n">
-        <v>74765</v>
+        <v>94690</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9135,30 +9144,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9244,10 +9254,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123312983</v>
+        <v>123313426</v>
       </c>
       <c r="B70" t="n">
-        <v>80443</v>
+        <v>94900</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9256,30 +9266,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>738</v>
+        <v>2668</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9287,10 +9298,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432217</v>
+        <v>432198</v>
       </c>
       <c r="R70" t="n">
-        <v>6152972</v>
+        <v>6152961</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9323,11 +9334,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9370,10 +9376,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313107</v>
+        <v>123313438</v>
       </c>
       <c r="B71" t="n">
-        <v>94879</v>
+        <v>74859</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9386,27 +9392,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9414,10 +9419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432268</v>
+        <v>432147</v>
       </c>
       <c r="R71" t="n">
-        <v>6152997</v>
+        <v>6152962</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9492,10 +9497,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313208</v>
+        <v>123313420</v>
       </c>
       <c r="B72" t="n">
-        <v>74770</v>
+        <v>74771</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9504,25 +9509,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1458</v>
+        <v>1118</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9535,10 +9540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432329</v>
+        <v>432198</v>
       </c>
       <c r="R72" t="n">
-        <v>6152963</v>
+        <v>6152961</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9585,17 +9590,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9613,10 +9618,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313092</v>
+        <v>123313365</v>
       </c>
       <c r="B73" t="n">
-        <v>80443</v>
+        <v>94690</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9625,38 +9630,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9664,10 +9662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432268</v>
+        <v>432240</v>
       </c>
       <c r="R73" t="n">
-        <v>6152997</v>
+        <v>6153018</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9702,11 +9700,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9719,17 +9712,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9747,10 +9740,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313365</v>
+        <v>123313425</v>
       </c>
       <c r="B74" t="n">
-        <v>94673</v>
+        <v>94896</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9763,21 +9756,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9791,10 +9784,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432240</v>
+        <v>432198</v>
       </c>
       <c r="R74" t="n">
-        <v>6153018</v>
+        <v>6152961</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9841,17 +9834,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9869,10 +9862,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313165</v>
+        <v>123313446</v>
       </c>
       <c r="B75" t="n">
-        <v>94673</v>
+        <v>79161</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9885,27 +9878,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9913,10 +9905,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R75" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9963,17 +9955,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9991,10 +9983,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313163</v>
+        <v>123313155</v>
       </c>
       <c r="B76" t="n">
-        <v>77111</v>
+        <v>110173</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10007,26 +9999,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1342</v>
+        <v>222776</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10072,11 +10069,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -10086,21 +10078,6 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>avenbok</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Carpinus betulus</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Carpinus betulus</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10117,10 +10094,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313105</v>
+        <v>123313422</v>
       </c>
       <c r="B77" t="n">
-        <v>94673</v>
+        <v>94690</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10161,10 +10138,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R77" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10239,10 +10216,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123312991</v>
+        <v>123313000</v>
       </c>
       <c r="B78" t="n">
-        <v>94879</v>
+        <v>94900</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10255,21 +10232,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10321,6 +10298,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10364,7 +10346,7 @@
         <v>123313362</v>
       </c>
       <c r="B79" t="n">
-        <v>74765</v>
+        <v>74771</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10487,10 +10469,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313000</v>
+        <v>123313107</v>
       </c>
       <c r="B80" t="n">
-        <v>94883</v>
+        <v>94896</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10503,21 +10485,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10531,10 +10513,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R80" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10567,11 +10549,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10614,10 +10591,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313426</v>
+        <v>123313092</v>
       </c>
       <c r="B81" t="n">
-        <v>94883</v>
+        <v>80449</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10626,31 +10603,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2668</v>
+        <v>738</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10658,10 +10642,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432198</v>
+        <v>432268</v>
       </c>
       <c r="R81" t="n">
-        <v>6152961</v>
+        <v>6152997</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10694,6 +10678,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10736,10 +10725,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313155</v>
+        <v>123312986</v>
       </c>
       <c r="B82" t="n">
-        <v>110156</v>
+        <v>94690</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10748,34 +10737,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222776</v>
+        <v>2779</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -10784,10 +10769,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432332</v>
+        <v>432217</v>
       </c>
       <c r="R82" t="n">
-        <v>6152958</v>
+        <v>6152972</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10831,6 +10816,21 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10847,10 +10847,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313109</v>
+        <v>123313105</v>
       </c>
       <c r="B83" t="n">
-        <v>94628</v>
+        <v>94690</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10863,21 +10863,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2676</v>
+        <v>2779</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10969,10 +10969,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313446</v>
+        <v>123313433</v>
       </c>
       <c r="B84" t="n">
-        <v>79155</v>
+        <v>74771</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6431</v>
+        <v>1118</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123313438</v>
+        <v>123313208</v>
       </c>
       <c r="B85" t="n">
-        <v>74853</v>
+        <v>74776</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11106,21 +11106,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6439</v>
+        <v>1458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432147</v>
+        <v>432329</v>
       </c>
       <c r="R85" t="n">
-        <v>6152962</v>
+        <v>6152963</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11183,17 +11183,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
         <v>123312996</v>
       </c>
       <c r="B86" t="n">
-        <v>94628</v>
+        <v>94645</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8884,10 +8884,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123312991</v>
+        <v>123313436</v>
       </c>
       <c r="B67" t="n">
-        <v>94896</v>
+        <v>94690</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8900,21 +8900,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432217</v>
+        <v>432147</v>
       </c>
       <c r="R67" t="n">
-        <v>6152972</v>
+        <v>6152962</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313163</v>
+        <v>123312991</v>
       </c>
       <c r="B68" t="n">
-        <v>77117</v>
+        <v>94896</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9018,30 +9018,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9049,10 +9050,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432332</v>
+        <v>432217</v>
       </c>
       <c r="R68" t="n">
-        <v>6152958</v>
+        <v>6152972</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9087,11 +9088,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9104,17 +9100,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9132,10 +9128,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313436</v>
+        <v>123313163</v>
       </c>
       <c r="B69" t="n">
-        <v>94690</v>
+        <v>77117</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9144,31 +9140,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9176,10 +9171,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R69" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9214,6 +9209,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9226,17 +9226,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -9618,10 +9618,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313365</v>
+        <v>123313425</v>
       </c>
       <c r="B73" t="n">
-        <v>94690</v>
+        <v>94896</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9634,21 +9634,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432240</v>
+        <v>432198</v>
       </c>
       <c r="R73" t="n">
-        <v>6153018</v>
+        <v>6152961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9712,17 +9712,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313425</v>
+        <v>123313365</v>
       </c>
       <c r="B74" t="n">
-        <v>94896</v>
+        <v>94690</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9756,21 +9756,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432198</v>
+        <v>432240</v>
       </c>
       <c r="R74" t="n">
-        <v>6152961</v>
+        <v>6153018</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9834,17 +9834,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9862,10 +9862,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313446</v>
+        <v>123313422</v>
       </c>
       <c r="B75" t="n">
-        <v>79161</v>
+        <v>94690</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9878,26 +9878,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9905,10 +9906,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R75" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9983,10 +9984,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313155</v>
+        <v>123313446</v>
       </c>
       <c r="B76" t="n">
-        <v>110173</v>
+        <v>79161</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9995,35 +9996,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222776</v>
+        <v>6431</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10031,10 +10027,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R76" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10078,6 +10074,21 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -10094,10 +10105,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313422</v>
+        <v>123313155</v>
       </c>
       <c r="B77" t="n">
-        <v>94690</v>
+        <v>110173</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10106,30 +10117,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2779</v>
+        <v>222776</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -10138,10 +10153,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432198</v>
+        <v>432332</v>
       </c>
       <c r="R77" t="n">
-        <v>6152961</v>
+        <v>6152958</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10185,21 +10200,6 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8884,10 +8884,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313436</v>
+        <v>123312991</v>
       </c>
       <c r="B67" t="n">
-        <v>94690</v>
+        <v>94896</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8900,21 +8900,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432147</v>
+        <v>432217</v>
       </c>
       <c r="R67" t="n">
-        <v>6152962</v>
+        <v>6152972</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123312991</v>
+        <v>123313163</v>
       </c>
       <c r="B68" t="n">
-        <v>94896</v>
+        <v>77117</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9018,31 +9018,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9050,10 +9049,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R68" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9088,6 +9087,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9100,17 +9104,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9128,10 +9132,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313163</v>
+        <v>123313436</v>
       </c>
       <c r="B69" t="n">
-        <v>77117</v>
+        <v>94690</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9140,30 +9144,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9171,10 +9176,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R69" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9209,11 +9214,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9226,17 +9226,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313425</v>
+        <v>123313365</v>
       </c>
       <c r="B73" t="n">
-        <v>94896</v>
+        <v>94690</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9634,21 +9634,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432198</v>
+        <v>432240</v>
       </c>
       <c r="R73" t="n">
-        <v>6152961</v>
+        <v>6153018</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9712,17 +9712,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313365</v>
+        <v>123313425</v>
       </c>
       <c r="B74" t="n">
-        <v>94690</v>
+        <v>94896</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9756,21 +9756,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432240</v>
+        <v>432198</v>
       </c>
       <c r="R74" t="n">
-        <v>6153018</v>
+        <v>6152961</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9834,17 +9834,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>123313165</v>
       </c>
       <c r="B62" t="n">
-        <v>94690</v>
+        <v>94696</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313167</v>
+        <v>123313107</v>
       </c>
       <c r="B63" t="n">
-        <v>74771</v>
+        <v>94902</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8398,30 +8398,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8429,10 +8430,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R63" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8479,17 +8480,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8507,10 +8508,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313384</v>
+        <v>123312983</v>
       </c>
       <c r="B64" t="n">
-        <v>80449</v>
+        <v>80454</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8540,16 +8541,8 @@
           <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -8558,10 +8551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R64" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8594,6 +8587,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8636,10 +8634,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313109</v>
+        <v>123313422</v>
       </c>
       <c r="B65" t="n">
-        <v>94645</v>
+        <v>94696</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8652,21 +8650,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2676</v>
+        <v>2779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8680,10 +8678,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R65" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8758,10 +8756,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123312983</v>
+        <v>123313000</v>
       </c>
       <c r="B66" t="n">
-        <v>80449</v>
+        <v>94906</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8770,30 +8768,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>738</v>
+        <v>2668</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8841,7 +8840,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8884,10 +8883,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123312991</v>
+        <v>123313167</v>
       </c>
       <c r="B67" t="n">
-        <v>94896</v>
+        <v>74774</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8896,31 +8895,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2667</v>
+        <v>1118</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8928,10 +8926,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R67" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8978,17 +8976,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9006,10 +9004,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313163</v>
+        <v>123313433</v>
       </c>
       <c r="B68" t="n">
-        <v>77117</v>
+        <v>74774</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9022,21 +9020,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9049,10 +9047,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R68" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9087,11 +9085,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9104,17 +9097,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9132,10 +9125,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313436</v>
+        <v>123313426</v>
       </c>
       <c r="B69" t="n">
-        <v>94690</v>
+        <v>94906</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9148,21 +9141,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9176,10 +9169,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R69" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9254,10 +9247,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123313426</v>
+        <v>123312991</v>
       </c>
       <c r="B70" t="n">
-        <v>94900</v>
+        <v>94902</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9270,21 +9263,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9298,10 +9291,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R70" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9376,10 +9369,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313438</v>
+        <v>123312986</v>
       </c>
       <c r="B71" t="n">
-        <v>74859</v>
+        <v>94696</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9392,26 +9385,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6439</v>
+        <v>2779</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9419,10 +9413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432147</v>
+        <v>432217</v>
       </c>
       <c r="R71" t="n">
-        <v>6152962</v>
+        <v>6152972</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9497,10 +9491,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313420</v>
+        <v>123313362</v>
       </c>
       <c r="B72" t="n">
-        <v>74771</v>
+        <v>74774</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9540,10 +9534,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432198</v>
+        <v>432240</v>
       </c>
       <c r="R72" t="n">
-        <v>6152961</v>
+        <v>6153018</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9578,6 +9572,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9590,17 +9589,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9618,10 +9617,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313365</v>
+        <v>123313109</v>
       </c>
       <c r="B73" t="n">
-        <v>94690</v>
+        <v>94651</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9634,21 +9633,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9662,10 +9661,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432240</v>
+        <v>432268</v>
       </c>
       <c r="R73" t="n">
-        <v>6153018</v>
+        <v>6152997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9712,17 +9711,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9740,10 +9739,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313425</v>
+        <v>123313420</v>
       </c>
       <c r="B74" t="n">
-        <v>94896</v>
+        <v>74774</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9752,31 +9751,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>1118</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9862,10 +9860,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313422</v>
+        <v>123313446</v>
       </c>
       <c r="B75" t="n">
-        <v>94690</v>
+        <v>79166</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9878,27 +9876,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9906,10 +9903,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R75" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9984,10 +9981,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313446</v>
+        <v>123313436</v>
       </c>
       <c r="B76" t="n">
-        <v>79161</v>
+        <v>94696</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10000,26 +9997,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10105,10 +10103,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313155</v>
+        <v>123313163</v>
       </c>
       <c r="B77" t="n">
-        <v>110173</v>
+        <v>77122</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10121,31 +10119,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222776</v>
+        <v>1342</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10191,6 +10184,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10200,6 +10198,21 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10216,10 +10229,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313000</v>
+        <v>123313365</v>
       </c>
       <c r="B78" t="n">
-        <v>94900</v>
+        <v>94696</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10232,21 +10245,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10260,10 +10273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432217</v>
+        <v>432240</v>
       </c>
       <c r="R78" t="n">
-        <v>6152972</v>
+        <v>6153018</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10298,11 +10311,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -10315,17 +10323,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10343,10 +10351,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313362</v>
+        <v>123313208</v>
       </c>
       <c r="B79" t="n">
-        <v>74771</v>
+        <v>74779</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10355,25 +10363,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1118</v>
+        <v>1458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10386,10 +10394,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432240</v>
+        <v>432329</v>
       </c>
       <c r="R79" t="n">
-        <v>6153018</v>
+        <v>6152963</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10424,11 +10432,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10441,17 +10444,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10469,10 +10472,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313107</v>
+        <v>123313438</v>
       </c>
       <c r="B80" t="n">
-        <v>94896</v>
+        <v>74862</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10485,27 +10488,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10513,10 +10515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432268</v>
+        <v>432147</v>
       </c>
       <c r="R80" t="n">
-        <v>6152997</v>
+        <v>6152962</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10591,10 +10593,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313092</v>
+        <v>123313384</v>
       </c>
       <c r="B81" t="n">
-        <v>80449</v>
+        <v>80454</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10626,7 +10628,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10642,10 +10644,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R81" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10678,11 +10680,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10725,10 +10722,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123312986</v>
+        <v>123313155</v>
       </c>
       <c r="B82" t="n">
-        <v>94690</v>
+        <v>110195</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,30 +10734,34 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2779</v>
+        <v>222776</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -10769,10 +10770,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R82" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10816,21 +10817,6 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10847,10 +10833,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313105</v>
+        <v>123313092</v>
       </c>
       <c r="B83" t="n">
-        <v>94690</v>
+        <v>80454</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10859,31 +10845,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10927,6 +10920,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10969,10 +10967,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313433</v>
+        <v>123313105</v>
       </c>
       <c r="B84" t="n">
-        <v>74771</v>
+        <v>94696</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10981,30 +10979,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11012,10 +11011,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432147</v>
+        <v>432268</v>
       </c>
       <c r="R84" t="n">
-        <v>6152962</v>
+        <v>6152997</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11090,10 +11089,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123313208</v>
+        <v>123313425</v>
       </c>
       <c r="B85" t="n">
-        <v>74776</v>
+        <v>94902</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11106,26 +11105,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1458</v>
+        <v>2667</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432329</v>
+        <v>432198</v>
       </c>
       <c r="R85" t="n">
-        <v>6152963</v>
+        <v>6152961</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11183,17 +11183,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
         <v>123312996</v>
       </c>
       <c r="B86" t="n">
-        <v>94645</v>
+        <v>94651</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7165,10 +7165,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102651018</v>
+        <v>86370074</v>
       </c>
       <c r="B53" t="n">
-        <v>103602</v>
+        <v>75910</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7177,49 +7177,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1331</v>
+        <v>1342</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pulmonaria officinalis</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Örups slott, Sk</t>
+          <t>400 m SV om Örups slott, Sk</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432384.5166894977</v>
+        <v>432588.3279796888</v>
       </c>
       <c r="R53" t="n">
-        <v>6152891.963480643</v>
+        <v>6153049.030289408</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7243,7 +7235,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>1988-05-25</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -7253,7 +7245,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>1988-05-25</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7261,40 +7253,43 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>många individ, men svårräknat</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Stefan Ekman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Ulf Arup, Stefan Ekman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>86370074</v>
+        <v>86370073</v>
       </c>
       <c r="B54" t="n">
-        <v>75910</v>
+        <v>75911</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7303,25 +7298,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Askvårtlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Pyrenula nitidella</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flörke ex Schaer.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7379,6 +7374,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>på 3 träd</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>86370073</v>
+        <v>86370075</v>
       </c>
       <c r="B55" t="n">
-        <v>75911</v>
+        <v>79158</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7424,25 +7424,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1343</v>
+        <v>1223</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Askvårtlav</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrenula nitidella</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Flörke ex Schaer.) Müll.Arg.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>på 3 träd</t>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7538,10 +7538,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>86370075</v>
+        <v>86370076</v>
       </c>
       <c r="B56" t="n">
-        <v>79158</v>
+        <v>73582</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7550,25 +7550,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1223</v>
+        <v>1118</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7626,11 +7626,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>sparsam</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7642,7 +7637,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>ask, avenbok, lönn</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7664,10 +7659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>86370076</v>
+        <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>73582</v>
+        <v>103602</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7676,41 +7671,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1118</v>
+        <v>1331</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Pulmonaria officinalis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>400 m SV om Örups slott, Sk</t>
+          <t>Almeskogen, intill NR, Sk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432588.3279796888</v>
+        <v>432378.6704156185</v>
       </c>
       <c r="R57" t="n">
-        <v>6153049.030289408</v>
+        <v>6152880.731607789</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1988-05-25</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1988-05-25</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -7752,6 +7752,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Några blommande plantor.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7761,34 +7766,30 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>ask, avenbok, lönn</t>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Gallrad lövskog.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Stefan Ekman</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulf Arup, Stefan Ekman</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Skyddsvärda lavar i sydvästra Sverige</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101475553</v>
+        <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>103602</v>
+        <v>104120</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7818,25 +7819,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Almeskogen, intill NR, Sk</t>
+          <t>Örup, Sk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432378.6704156185</v>
+        <v>432299</v>
       </c>
       <c r="R58" t="n">
-        <v>6152880.731607789</v>
+        <v>6152867</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7860,27 +7868,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Några blommande plantor.</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7889,33 +7882,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Gallrad lövskog.</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Petra Alinder</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Petra Alinder</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111942881</v>
+        <v>116865233</v>
       </c>
       <c r="B59" t="n">
-        <v>104120</v>
+        <v>80108</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7928,46 +7917,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1331</v>
+        <v>738</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pulmonaria officinalis</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Örup, Sk</t>
+          <t>Almlav, Sk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>432299</v>
+        <v>432209</v>
       </c>
       <c r="R59" t="n">
-        <v>6152867</v>
+        <v>6152970</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7994,12 +7974,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8012,25 +7992,40 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Petra Alinder</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Petra Alinder</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>116865233</v>
+        <v>122879089</v>
       </c>
       <c r="B60" t="n">
-        <v>80108</v>
+        <v>80443</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8066,14 +8061,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Almlav, Sk</t>
+          <t>Bennestad, Almskog, Sk</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432209</v>
+        <v>432213</v>
       </c>
       <c r="R60" t="n">
-        <v>6152970</v>
+        <v>6152973</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -8100,12 +8095,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8118,40 +8113,35 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Skogslönn</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Skogslönn</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
+          <t>Kristian Gärdsborn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
+          <t>Kristian Gärdsborn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122879089</v>
+        <v>123313109</v>
       </c>
       <c r="B61" t="n">
-        <v>80443</v>
+        <v>94653</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8160,44 +8150,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>738</v>
+        <v>2676</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bennestad, Almskog, Sk</t>
+          <t>Örup, Sk</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432213</v>
+        <v>432268</v>
       </c>
       <c r="R61" t="n">
-        <v>6152973</v>
+        <v>6152997</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8221,12 +8212,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8239,35 +8230,40 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>Skogslönn</t>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Skogslönn</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Gärdsborn</t>
+          <t>Alex Regnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Gärdsborn</t>
+          <t>Alex Regnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313165</v>
+        <v>123313000</v>
       </c>
       <c r="B62" t="n">
-        <v>94696</v>
+        <v>94908</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8280,21 +8276,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8308,10 +8304,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432332</v>
+        <v>432217</v>
       </c>
       <c r="R62" t="n">
-        <v>6152958</v>
+        <v>6152972</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8346,6 +8342,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8358,17 +8359,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8386,10 +8387,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313107</v>
+        <v>123313384</v>
       </c>
       <c r="B63" t="n">
-        <v>94902</v>
+        <v>80456</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8398,31 +8399,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>738</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8430,10 +8438,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R63" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8508,10 +8516,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123312983</v>
+        <v>123313436</v>
       </c>
       <c r="B64" t="n">
-        <v>80454</v>
+        <v>94698</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8520,30 +8528,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8551,10 +8560,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432217</v>
+        <v>432147</v>
       </c>
       <c r="R64" t="n">
-        <v>6152972</v>
+        <v>6152962</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8587,11 +8596,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8634,10 +8638,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313422</v>
+        <v>123313438</v>
       </c>
       <c r="B65" t="n">
-        <v>94696</v>
+        <v>74863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8650,27 +8654,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2779</v>
+        <v>6439</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8678,10 +8681,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R65" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8756,10 +8759,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313000</v>
+        <v>123313155</v>
       </c>
       <c r="B66" t="n">
-        <v>94906</v>
+        <v>110197</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8768,30 +8771,34 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2668</v>
+        <v>222776</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -8800,10 +8807,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R66" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8838,11 +8845,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8852,21 +8854,6 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8883,10 +8870,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313167</v>
+        <v>123313422</v>
       </c>
       <c r="B67" t="n">
-        <v>74774</v>
+        <v>94698</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8895,30 +8882,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8926,10 +8914,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R67" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8976,17 +8964,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9004,10 +8992,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313433</v>
+        <v>123313167</v>
       </c>
       <c r="B68" t="n">
-        <v>74774</v>
+        <v>74775</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9047,10 +9035,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R68" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9097,17 +9085,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9125,10 +9113,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313426</v>
+        <v>123312986</v>
       </c>
       <c r="B69" t="n">
-        <v>94906</v>
+        <v>94698</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9141,21 +9129,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2668</v>
+        <v>2779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9169,10 +9157,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R69" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9247,10 +9235,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123312991</v>
+        <v>123313426</v>
       </c>
       <c r="B70" t="n">
-        <v>94902</v>
+        <v>94908</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9263,21 +9251,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9291,10 +9279,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432217</v>
+        <v>432198</v>
       </c>
       <c r="R70" t="n">
-        <v>6152972</v>
+        <v>6152961</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9369,10 +9357,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123312986</v>
+        <v>123312983</v>
       </c>
       <c r="B71" t="n">
-        <v>94696</v>
+        <v>80456</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9381,31 +9369,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9449,6 +9436,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9491,10 +9483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313362</v>
+        <v>123313446</v>
       </c>
       <c r="B72" t="n">
-        <v>74774</v>
+        <v>79168</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9503,25 +9495,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1118</v>
+        <v>6431</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9534,10 +9526,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432240</v>
+        <v>432147</v>
       </c>
       <c r="R72" t="n">
-        <v>6153018</v>
+        <v>6152962</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9572,11 +9564,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9589,17 +9576,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9617,10 +9604,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313109</v>
+        <v>123313163</v>
       </c>
       <c r="B73" t="n">
-        <v>94651</v>
+        <v>77124</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9629,31 +9616,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2676</v>
+        <v>1342</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9661,10 +9647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432268</v>
+        <v>432332</v>
       </c>
       <c r="R73" t="n">
-        <v>6152997</v>
+        <v>6152958</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9699,6 +9685,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9711,17 +9702,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9739,10 +9730,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313420</v>
+        <v>123313433</v>
       </c>
       <c r="B74" t="n">
-        <v>74774</v>
+        <v>74775</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9782,10 +9773,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R74" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9860,10 +9851,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313446</v>
+        <v>123313365</v>
       </c>
       <c r="B75" t="n">
-        <v>79166</v>
+        <v>94698</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9876,26 +9867,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9903,10 +9895,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432147</v>
+        <v>432240</v>
       </c>
       <c r="R75" t="n">
-        <v>6152962</v>
+        <v>6153018</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9953,17 +9945,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9981,10 +9973,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313436</v>
+        <v>123313420</v>
       </c>
       <c r="B76" t="n">
-        <v>94696</v>
+        <v>74775</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9993,31 +9985,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2779</v>
+        <v>1118</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10025,10 +10016,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R76" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10103,10 +10094,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313163</v>
+        <v>123313107</v>
       </c>
       <c r="B77" t="n">
-        <v>77122</v>
+        <v>94904</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10115,30 +10106,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10146,10 +10138,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R77" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10184,11 +10176,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -10201,17 +10188,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10229,10 +10216,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313365</v>
+        <v>123312991</v>
       </c>
       <c r="B78" t="n">
-        <v>94696</v>
+        <v>94904</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10245,21 +10232,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10273,10 +10260,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432240</v>
+        <v>432217</v>
       </c>
       <c r="R78" t="n">
-        <v>6153018</v>
+        <v>6152972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10323,17 +10310,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10351,10 +10338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313208</v>
+        <v>123313092</v>
       </c>
       <c r="B79" t="n">
-        <v>74779</v>
+        <v>80456</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10363,29 +10350,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1458</v>
+        <v>738</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -10394,10 +10389,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432329</v>
+        <v>432268</v>
       </c>
       <c r="R79" t="n">
-        <v>6152963</v>
+        <v>6152997</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10432,6 +10427,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -10444,17 +10444,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10472,10 +10472,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313438</v>
+        <v>123313362</v>
       </c>
       <c r="B80" t="n">
-        <v>74862</v>
+        <v>74775</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10484,25 +10484,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6439</v>
+        <v>1118</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10515,10 +10515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432147</v>
+        <v>432240</v>
       </c>
       <c r="R80" t="n">
-        <v>6152962</v>
+        <v>6153018</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10553,6 +10553,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10565,17 +10570,17 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10593,10 +10598,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313384</v>
+        <v>123313165</v>
       </c>
       <c r="B81" t="n">
-        <v>80454</v>
+        <v>94698</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10605,38 +10610,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10644,10 +10642,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432198</v>
+        <v>432332</v>
       </c>
       <c r="R81" t="n">
-        <v>6152961</v>
+        <v>6152958</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10694,17 +10692,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10722,10 +10720,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313155</v>
+        <v>123313208</v>
       </c>
       <c r="B82" t="n">
-        <v>110195</v>
+        <v>74780</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10734,35 +10732,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222776</v>
+        <v>1458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10770,10 +10763,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432332</v>
+        <v>432329</v>
       </c>
       <c r="R82" t="n">
-        <v>6152958</v>
+        <v>6152963</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10817,6 +10810,21 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10833,10 +10841,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313092</v>
+        <v>123313425</v>
       </c>
       <c r="B83" t="n">
-        <v>80454</v>
+        <v>94904</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10845,38 +10853,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10884,10 +10885,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R83" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10920,11 +10921,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10970,7 +10966,7 @@
         <v>123313105</v>
       </c>
       <c r="B84" t="n">
-        <v>94696</v>
+        <v>94698</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11089,14 +11085,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123313425</v>
+        <v>123312996</v>
       </c>
       <c r="B85" t="n">
-        <v>94902</v>
+        <v>94653</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11105,21 +11101,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2667</v>
+        <v>2676</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11133,10 +11129,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R85" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11171,6 +11167,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11208,133 +11209,6 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>123312996</v>
-      </c>
-      <c r="B86" t="n">
-        <v>94651</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>2676</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Grov baronmossa</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Anomodon viticulosus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Örup, Sk</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>432217</v>
-      </c>
-      <c r="R86" t="n">
-        <v>6152972</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Tomelilla</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Benestad</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF86" t="inlineStr"/>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Alex Regnér</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Alex Regnér</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -10216,10 +10216,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123312991</v>
+        <v>123313092</v>
       </c>
       <c r="B78" t="n">
-        <v>94904</v>
+        <v>80456</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10228,31 +10228,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2667</v>
+        <v>738</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10260,10 +10267,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R78" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10296,6 +10303,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10338,10 +10350,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313092</v>
+        <v>123312991</v>
       </c>
       <c r="B79" t="n">
-        <v>80456</v>
+        <v>94904</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10350,38 +10362,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10389,10 +10394,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R79" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10425,11 +10430,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -9604,10 +9604,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313163</v>
+        <v>123313433</v>
       </c>
       <c r="B73" t="n">
-        <v>77124</v>
+        <v>74775</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9620,21 +9620,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9647,10 +9647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R73" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9685,11 +9685,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9702,17 +9697,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9730,10 +9725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313433</v>
+        <v>123313365</v>
       </c>
       <c r="B74" t="n">
-        <v>74775</v>
+        <v>94698</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9742,30 +9737,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9773,10 +9769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432147</v>
+        <v>432240</v>
       </c>
       <c r="R74" t="n">
-        <v>6152962</v>
+        <v>6153018</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9823,17 +9819,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9851,10 +9847,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313365</v>
+        <v>123313163</v>
       </c>
       <c r="B75" t="n">
-        <v>94698</v>
+        <v>77124</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9863,31 +9859,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9895,10 +9890,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432240</v>
+        <v>432332</v>
       </c>
       <c r="R75" t="n">
-        <v>6153018</v>
+        <v>6152958</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9931,6 +9926,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10216,10 +10216,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313092</v>
+        <v>123312991</v>
       </c>
       <c r="B78" t="n">
-        <v>80456</v>
+        <v>94904</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10228,38 +10228,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10267,10 +10260,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R78" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10303,11 +10296,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10350,10 +10338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123312991</v>
+        <v>123313092</v>
       </c>
       <c r="B79" t="n">
-        <v>94904</v>
+        <v>80456</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10362,31 +10350,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2667</v>
+        <v>738</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10394,10 +10389,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R79" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10430,6 +10425,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8138,10 +8138,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123313109</v>
+        <v>123312986</v>
       </c>
       <c r="B61" t="n">
-        <v>94653</v>
+        <v>95206</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8154,21 +8154,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2676</v>
+        <v>2779</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R61" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313000</v>
+        <v>123313438</v>
       </c>
       <c r="B62" t="n">
-        <v>94908</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8276,27 +8276,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2668</v>
+        <v>6439</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8304,10 +8303,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432217</v>
+        <v>432147</v>
       </c>
       <c r="R62" t="n">
-        <v>6152972</v>
+        <v>6152962</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8340,11 +8339,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8387,10 +8381,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313384</v>
+        <v>123313000</v>
       </c>
       <c r="B63" t="n">
-        <v>80456</v>
+        <v>95416</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8399,38 +8393,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>738</v>
+        <v>2668</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8438,10 +8425,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R63" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8474,6 +8461,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8516,10 +8508,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313436</v>
+        <v>123313208</v>
       </c>
       <c r="B64" t="n">
-        <v>94698</v>
+        <v>74780</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8532,27 +8524,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2779</v>
+        <v>1458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8560,10 +8551,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432147</v>
+        <v>432329</v>
       </c>
       <c r="R64" t="n">
-        <v>6152962</v>
+        <v>6152963</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8610,17 +8601,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8638,10 +8629,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313438</v>
+        <v>123313155</v>
       </c>
       <c r="B65" t="n">
-        <v>74863</v>
+        <v>109772</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8650,30 +8641,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6439</v>
+        <v>222776</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8681,10 +8677,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R65" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8728,21 +8724,6 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8759,10 +8740,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313155</v>
+        <v>123313167</v>
       </c>
       <c r="B66" t="n">
-        <v>110197</v>
+        <v>74775</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8775,31 +8756,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222776</v>
+        <v>1118</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8854,6 +8830,21 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8870,10 +8861,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313422</v>
+        <v>123313365</v>
       </c>
       <c r="B67" t="n">
-        <v>94698</v>
+        <v>95206</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8914,10 +8905,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432198</v>
+        <v>432240</v>
       </c>
       <c r="R67" t="n">
-        <v>6152961</v>
+        <v>6153018</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8964,17 +8955,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8992,7 +8983,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313167</v>
+        <v>123313362</v>
       </c>
       <c r="B68" t="n">
         <v>74775</v>
@@ -9035,10 +9026,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432332</v>
+        <v>432240</v>
       </c>
       <c r="R68" t="n">
-        <v>6152958</v>
+        <v>6153018</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9071,6 +9062,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9113,10 +9109,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123312986</v>
+        <v>123313422</v>
       </c>
       <c r="B69" t="n">
-        <v>94698</v>
+        <v>95206</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9157,10 +9153,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432217</v>
+        <v>432198</v>
       </c>
       <c r="R69" t="n">
-        <v>6152972</v>
+        <v>6152961</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9235,10 +9231,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123313426</v>
+        <v>123312983</v>
       </c>
       <c r="B70" t="n">
-        <v>94908</v>
+        <v>80456</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9247,31 +9243,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2668</v>
+        <v>738</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9279,10 +9274,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R70" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9315,6 +9310,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123312983</v>
+        <v>123313425</v>
       </c>
       <c r="B71" t="n">
-        <v>80456</v>
+        <v>95412</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9369,30 +9369,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9400,10 +9401,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432217</v>
+        <v>432198</v>
       </c>
       <c r="R71" t="n">
-        <v>6152972</v>
+        <v>6152961</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9436,11 +9437,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9483,10 +9479,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313446</v>
+        <v>123313436</v>
       </c>
       <c r="B72" t="n">
-        <v>79168</v>
+        <v>95206</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9499,26 +9495,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9604,10 +9601,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313433</v>
+        <v>123313384</v>
       </c>
       <c r="B73" t="n">
-        <v>74775</v>
+        <v>80456</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9616,29 +9613,37 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9647,10 +9652,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R73" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9725,10 +9730,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313365</v>
+        <v>123313109</v>
       </c>
       <c r="B74" t="n">
-        <v>94698</v>
+        <v>95161</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9741,21 +9746,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9769,10 +9774,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432240</v>
+        <v>432268</v>
       </c>
       <c r="R74" t="n">
-        <v>6153018</v>
+        <v>6152997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9819,17 +9824,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9973,10 +9978,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313420</v>
+        <v>123313446</v>
       </c>
       <c r="B76" t="n">
-        <v>74775</v>
+        <v>79168</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9985,25 +9990,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1118</v>
+        <v>6431</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10016,10 +10021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R76" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10094,10 +10099,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313107</v>
+        <v>123312991</v>
       </c>
       <c r="B77" t="n">
-        <v>94904</v>
+        <v>95412</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10138,10 +10143,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R77" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10216,10 +10221,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123312991</v>
+        <v>123313165</v>
       </c>
       <c r="B78" t="n">
-        <v>94904</v>
+        <v>95206</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10232,21 +10237,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10260,10 +10265,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R78" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10310,17 +10315,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10338,10 +10343,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313092</v>
+        <v>123313105</v>
       </c>
       <c r="B79" t="n">
-        <v>80456</v>
+        <v>95206</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10350,38 +10355,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10425,11 +10423,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10472,10 +10465,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313362</v>
+        <v>123313426</v>
       </c>
       <c r="B80" t="n">
-        <v>74775</v>
+        <v>95416</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10484,30 +10477,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1118</v>
+        <v>2668</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10515,10 +10509,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432240</v>
+        <v>432198</v>
       </c>
       <c r="R80" t="n">
-        <v>6153018</v>
+        <v>6152961</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10553,11 +10547,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10570,17 +10559,17 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10598,10 +10587,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313165</v>
+        <v>123313092</v>
       </c>
       <c r="B81" t="n">
-        <v>94698</v>
+        <v>80456</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10610,31 +10599,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10642,10 +10638,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R81" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10680,6 +10676,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10692,17 +10693,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10720,10 +10721,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313208</v>
+        <v>123313107</v>
       </c>
       <c r="B82" t="n">
-        <v>74780</v>
+        <v>95412</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10736,26 +10737,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1458</v>
+        <v>2667</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10763,10 +10765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432329</v>
+        <v>432268</v>
       </c>
       <c r="R82" t="n">
-        <v>6152963</v>
+        <v>6152997</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10813,17 +10815,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10841,10 +10843,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313425</v>
+        <v>123313433</v>
       </c>
       <c r="B83" t="n">
-        <v>94904</v>
+        <v>74775</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10853,31 +10855,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>1118</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10885,10 +10886,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R83" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10963,10 +10964,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313105</v>
+        <v>123313420</v>
       </c>
       <c r="B84" t="n">
-        <v>94698</v>
+        <v>74775</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10975,31 +10976,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>1118</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R84" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11088,7 +11088,7 @@
         <v>123312996</v>
       </c>
       <c r="B85" t="n">
-        <v>94653</v>
+        <v>95161</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8138,10 +8138,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123312986</v>
+        <v>123313426</v>
       </c>
       <c r="B61" t="n">
-        <v>95206</v>
+        <v>95416</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8154,21 +8154,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432217</v>
+        <v>432198</v>
       </c>
       <c r="R61" t="n">
-        <v>6152972</v>
+        <v>6152961</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313438</v>
+        <v>123313105</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>95206</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8276,26 +8276,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6439</v>
+        <v>2779</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8303,10 +8304,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432147</v>
+        <v>432268</v>
       </c>
       <c r="R62" t="n">
-        <v>6152962</v>
+        <v>6152997</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8381,10 +8382,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313000</v>
+        <v>123313438</v>
       </c>
       <c r="B63" t="n">
-        <v>95416</v>
+        <v>74863</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8397,27 +8398,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2668</v>
+        <v>6439</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8425,10 +8425,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432217</v>
+        <v>432147</v>
       </c>
       <c r="R63" t="n">
-        <v>6152972</v>
+        <v>6152962</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8461,11 +8461,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8508,10 +8503,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313208</v>
+        <v>123313163</v>
       </c>
       <c r="B64" t="n">
-        <v>74780</v>
+        <v>77124</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8520,25 +8515,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1458</v>
+        <v>1342</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8551,10 +8546,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432329</v>
+        <v>432332</v>
       </c>
       <c r="R64" t="n">
-        <v>6152963</v>
+        <v>6152958</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8589,6 +8584,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8601,17 +8601,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313155</v>
+        <v>123313109</v>
       </c>
       <c r="B65" t="n">
-        <v>109772</v>
+        <v>95161</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8641,34 +8641,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222776</v>
+        <v>2676</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -8677,10 +8673,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R65" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8724,6 +8720,21 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8740,10 +8751,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313167</v>
+        <v>123313436</v>
       </c>
       <c r="B66" t="n">
-        <v>74775</v>
+        <v>95206</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8752,30 +8763,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8783,10 +8795,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432332</v>
+        <v>432147</v>
       </c>
       <c r="R66" t="n">
-        <v>6152958</v>
+        <v>6152962</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8833,17 +8845,17 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8861,10 +8873,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313365</v>
+        <v>123313446</v>
       </c>
       <c r="B67" t="n">
-        <v>95206</v>
+        <v>79168</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8877,27 +8889,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8905,10 +8916,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432240</v>
+        <v>432147</v>
       </c>
       <c r="R67" t="n">
-        <v>6153018</v>
+        <v>6152962</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8955,17 +8966,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9109,10 +9120,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313422</v>
+        <v>123313000</v>
       </c>
       <c r="B69" t="n">
-        <v>95206</v>
+        <v>95416</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9125,21 +9136,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9153,10 +9164,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R69" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9189,6 +9200,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9231,10 +9247,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123312983</v>
+        <v>123313208</v>
       </c>
       <c r="B70" t="n">
-        <v>80456</v>
+        <v>74780</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9243,25 +9259,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>738</v>
+        <v>1458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9274,10 +9290,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432217</v>
+        <v>432329</v>
       </c>
       <c r="R70" t="n">
-        <v>6152972</v>
+        <v>6152963</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9312,11 +9328,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9329,17 +9340,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9357,10 +9368,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313425</v>
+        <v>123313155</v>
       </c>
       <c r="B71" t="n">
-        <v>95412</v>
+        <v>109772</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9369,30 +9380,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2667</v>
+        <v>222776</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -9401,10 +9416,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432198</v>
+        <v>432332</v>
       </c>
       <c r="R71" t="n">
-        <v>6152961</v>
+        <v>6152958</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9448,21 +9463,6 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9479,10 +9479,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313436</v>
+        <v>123312991</v>
       </c>
       <c r="B72" t="n">
-        <v>95206</v>
+        <v>95412</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9495,21 +9495,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9523,10 +9523,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432147</v>
+        <v>432217</v>
       </c>
       <c r="R72" t="n">
-        <v>6152962</v>
+        <v>6152972</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9601,10 +9601,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313384</v>
+        <v>123313433</v>
       </c>
       <c r="B73" t="n">
-        <v>80456</v>
+        <v>74775</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9613,37 +9613,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>738</v>
+        <v>1118</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Kunze) J.R.Laundon</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
@@ -9652,10 +9644,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R73" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9730,10 +9722,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313109</v>
+        <v>123312986</v>
       </c>
       <c r="B74" t="n">
-        <v>95161</v>
+        <v>95206</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9746,21 +9738,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2676</v>
+        <v>2779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9774,10 +9766,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R74" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9852,10 +9844,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313163</v>
+        <v>123313420</v>
       </c>
       <c r="B75" t="n">
-        <v>77124</v>
+        <v>74775</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9868,21 +9860,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9895,10 +9887,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R75" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9933,11 +9925,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9950,17 +9937,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9978,10 +9965,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313446</v>
+        <v>123313422</v>
       </c>
       <c r="B76" t="n">
-        <v>79168</v>
+        <v>95206</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9994,26 +9981,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10021,10 +10009,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432147</v>
+        <v>432198</v>
       </c>
       <c r="R76" t="n">
-        <v>6152962</v>
+        <v>6152961</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10099,10 +10087,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123312991</v>
+        <v>123313167</v>
       </c>
       <c r="B77" t="n">
-        <v>95412</v>
+        <v>74775</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10111,31 +10099,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2667</v>
+        <v>1118</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10143,10 +10130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R77" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10193,17 +10180,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10221,10 +10208,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313165</v>
+        <v>123313384</v>
       </c>
       <c r="B78" t="n">
-        <v>95206</v>
+        <v>80456</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10233,31 +10220,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10265,10 +10259,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R78" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10315,17 +10309,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10343,10 +10337,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313105</v>
+        <v>123313092</v>
       </c>
       <c r="B79" t="n">
-        <v>95206</v>
+        <v>80456</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10355,31 +10349,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10423,6 +10424,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10465,10 +10471,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313426</v>
+        <v>123313425</v>
       </c>
       <c r="B80" t="n">
-        <v>95416</v>
+        <v>95412</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10481,21 +10487,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10587,10 +10593,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313092</v>
+        <v>123313107</v>
       </c>
       <c r="B81" t="n">
-        <v>80456</v>
+        <v>95412</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10599,38 +10605,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10674,11 +10673,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10721,10 +10715,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313107</v>
+        <v>123313365</v>
       </c>
       <c r="B82" t="n">
-        <v>95412</v>
+        <v>95206</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10737,21 +10731,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10765,10 +10759,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432268</v>
+        <v>432240</v>
       </c>
       <c r="R82" t="n">
-        <v>6152997</v>
+        <v>6153018</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10815,17 +10809,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10843,10 +10837,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313433</v>
+        <v>123313165</v>
       </c>
       <c r="B83" t="n">
-        <v>74775</v>
+        <v>95206</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10855,30 +10849,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10886,10 +10881,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R83" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10936,17 +10931,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10964,10 +10959,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313420</v>
+        <v>123312983</v>
       </c>
       <c r="B84" t="n">
-        <v>74775</v>
+        <v>80456</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10976,25 +10971,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11007,10 +11002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R84" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11043,6 +11038,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8138,10 +8138,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123313426</v>
+        <v>123313107</v>
       </c>
       <c r="B61" t="n">
-        <v>95416</v>
+        <v>95412</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8154,21 +8154,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432198</v>
+        <v>432268</v>
       </c>
       <c r="R61" t="n">
-        <v>6152961</v>
+        <v>6152997</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8260,7 +8260,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313105</v>
+        <v>123313365</v>
       </c>
       <c r="B62" t="n">
         <v>95206</v>
@@ -8304,10 +8304,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432268</v>
+        <v>432240</v>
       </c>
       <c r="R62" t="n">
-        <v>6152997</v>
+        <v>6153018</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8354,17 +8354,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313438</v>
+        <v>123313446</v>
       </c>
       <c r="B63" t="n">
-        <v>74863</v>
+        <v>79168</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6439</v>
+        <v>6431</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8503,10 +8503,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313163</v>
+        <v>123313208</v>
       </c>
       <c r="B64" t="n">
-        <v>77124</v>
+        <v>74780</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8515,25 +8515,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1342</v>
+        <v>1458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8546,10 +8546,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432332</v>
+        <v>432329</v>
       </c>
       <c r="R64" t="n">
-        <v>6152958</v>
+        <v>6152963</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8584,11 +8584,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8601,17 +8596,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8629,10 +8624,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313109</v>
+        <v>123313425</v>
       </c>
       <c r="B65" t="n">
-        <v>95161</v>
+        <v>95412</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8645,21 +8640,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2676</v>
+        <v>2667</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8673,10 +8668,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R65" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8751,10 +8746,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313436</v>
+        <v>123313438</v>
       </c>
       <c r="B66" t="n">
-        <v>95206</v>
+        <v>74863</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8767,27 +8762,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2779</v>
+        <v>6439</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8873,10 +8867,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313446</v>
+        <v>123313167</v>
       </c>
       <c r="B67" t="n">
-        <v>79168</v>
+        <v>74775</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8885,25 +8879,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6431</v>
+        <v>1118</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8916,10 +8910,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R67" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8966,17 +8960,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8994,7 +8988,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313362</v>
+        <v>123313433</v>
       </c>
       <c r="B68" t="n">
         <v>74775</v>
@@ -9037,10 +9031,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432240</v>
+        <v>432147</v>
       </c>
       <c r="R68" t="n">
-        <v>6153018</v>
+        <v>6152962</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9075,11 +9069,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9092,17 +9081,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9120,10 +9109,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313000</v>
+        <v>123313362</v>
       </c>
       <c r="B69" t="n">
-        <v>95416</v>
+        <v>74775</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9132,31 +9121,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2668</v>
+        <v>1118</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9164,10 +9152,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432217</v>
+        <v>432240</v>
       </c>
       <c r="R69" t="n">
-        <v>6152972</v>
+        <v>6153018</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9204,7 +9192,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Gammal avenbok</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9219,17 +9207,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9247,10 +9235,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123313208</v>
+        <v>123313436</v>
       </c>
       <c r="B70" t="n">
-        <v>74780</v>
+        <v>95206</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9263,26 +9251,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1458</v>
+        <v>2779</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9290,10 +9279,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432329</v>
+        <v>432147</v>
       </c>
       <c r="R70" t="n">
-        <v>6152963</v>
+        <v>6152962</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9340,17 +9329,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9368,10 +9357,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313155</v>
+        <v>123313000</v>
       </c>
       <c r="B71" t="n">
-        <v>109772</v>
+        <v>95416</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9380,34 +9369,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222776</v>
+        <v>2668</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -9416,10 +9401,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432332</v>
+        <v>432217</v>
       </c>
       <c r="R71" t="n">
-        <v>6152958</v>
+        <v>6152972</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9454,6 +9439,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9463,6 +9453,21 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9479,10 +9484,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123312991</v>
+        <v>123313163</v>
       </c>
       <c r="B72" t="n">
-        <v>95412</v>
+        <v>77124</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9491,31 +9496,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9523,10 +9527,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R72" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9561,6 +9565,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9573,17 +9582,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9601,10 +9610,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313433</v>
+        <v>123313109</v>
       </c>
       <c r="B73" t="n">
-        <v>74775</v>
+        <v>95161</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9613,30 +9622,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1118</v>
+        <v>2676</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9644,10 +9654,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432147</v>
+        <v>432268</v>
       </c>
       <c r="R73" t="n">
-        <v>6152962</v>
+        <v>6152997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9722,10 +9732,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123312986</v>
+        <v>123313092</v>
       </c>
       <c r="B74" t="n">
-        <v>95206</v>
+        <v>80456</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9734,31 +9744,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9766,10 +9783,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R74" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9802,6 +9819,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9844,10 +9866,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123313420</v>
+        <v>123312991</v>
       </c>
       <c r="B75" t="n">
-        <v>74775</v>
+        <v>95412</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9856,30 +9878,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9887,10 +9910,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R75" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9965,10 +9988,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123313422</v>
+        <v>123313426</v>
       </c>
       <c r="B76" t="n">
-        <v>95206</v>
+        <v>95416</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9981,21 +10004,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10087,7 +10110,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313167</v>
+        <v>123313420</v>
       </c>
       <c r="B77" t="n">
         <v>74775</v>
@@ -10130,10 +10153,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R77" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10180,17 +10203,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10208,7 +10231,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123313384</v>
+        <v>123312983</v>
       </c>
       <c r="B78" t="n">
         <v>80456</v>
@@ -10241,16 +10264,8 @@
           <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
@@ -10259,10 +10274,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432198</v>
+        <v>432217</v>
       </c>
       <c r="R78" t="n">
-        <v>6152961</v>
+        <v>6152972</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10295,6 +10310,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10337,10 +10357,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313092</v>
+        <v>123313105</v>
       </c>
       <c r="B79" t="n">
-        <v>80456</v>
+        <v>95206</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10349,38 +10369,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10424,11 +10437,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10471,10 +10479,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313425</v>
+        <v>123313155</v>
       </c>
       <c r="B80" t="n">
-        <v>95412</v>
+        <v>109775</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10483,30 +10491,34 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2667</v>
+        <v>222776</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -10515,10 +10527,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432198</v>
+        <v>432332</v>
       </c>
       <c r="R80" t="n">
-        <v>6152961</v>
+        <v>6152958</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10562,21 +10574,6 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10593,10 +10590,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123313107</v>
+        <v>123312986</v>
       </c>
       <c r="B81" t="n">
-        <v>95412</v>
+        <v>95206</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10609,21 +10606,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10637,10 +10634,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R81" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10715,7 +10712,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313365</v>
+        <v>123313422</v>
       </c>
       <c r="B82" t="n">
         <v>95206</v>
@@ -10759,10 +10756,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432240</v>
+        <v>432198</v>
       </c>
       <c r="R82" t="n">
-        <v>6153018</v>
+        <v>6152961</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10809,17 +10806,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10837,10 +10834,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313165</v>
+        <v>123313384</v>
       </c>
       <c r="B83" t="n">
-        <v>95206</v>
+        <v>80456</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10849,31 +10846,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2779</v>
+        <v>738</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -10881,10 +10885,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R83" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10931,17 +10935,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10959,10 +10963,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123312983</v>
+        <v>123313165</v>
       </c>
       <c r="B84" t="n">
-        <v>80456</v>
+        <v>95206</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10971,30 +10975,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>738</v>
+        <v>2779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11002,10 +11007,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R84" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11040,11 +11045,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11057,17 +11057,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -8138,10 +8138,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123313107</v>
+        <v>123313365</v>
       </c>
       <c r="B61" t="n">
-        <v>95412</v>
+        <v>95206</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8154,21 +8154,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432268</v>
+        <v>432240</v>
       </c>
       <c r="R61" t="n">
-        <v>6152997</v>
+        <v>6153018</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8232,17 +8232,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123313365</v>
+        <v>123313155</v>
       </c>
       <c r="B62" t="n">
-        <v>95206</v>
+        <v>109776</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8272,30 +8272,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2779</v>
+        <v>222776</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -8304,10 +8308,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432240</v>
+        <v>432332</v>
       </c>
       <c r="R62" t="n">
-        <v>6153018</v>
+        <v>6152958</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8351,21 +8355,6 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>avenbok</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Carpinus betulus</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Carpinus betulus</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8382,10 +8371,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123313446</v>
+        <v>123313436</v>
       </c>
       <c r="B63" t="n">
-        <v>79168</v>
+        <v>95206</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8398,26 +8387,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8503,10 +8493,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123313208</v>
+        <v>123313362</v>
       </c>
       <c r="B64" t="n">
-        <v>74780</v>
+        <v>74775</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8515,25 +8505,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1458</v>
+        <v>1118</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8546,10 +8536,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432329</v>
+        <v>432240</v>
       </c>
       <c r="R64" t="n">
-        <v>6152963</v>
+        <v>6153018</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8584,6 +8574,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8596,17 +8591,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8624,10 +8619,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123313425</v>
+        <v>123313109</v>
       </c>
       <c r="B65" t="n">
-        <v>95412</v>
+        <v>95161</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8640,21 +8635,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2667</v>
+        <v>2676</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8668,10 +8663,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432198</v>
+        <v>432268</v>
       </c>
       <c r="R65" t="n">
-        <v>6152961</v>
+        <v>6152997</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8746,10 +8741,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123313438</v>
+        <v>123313165</v>
       </c>
       <c r="B66" t="n">
-        <v>74863</v>
+        <v>95206</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8762,26 +8757,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6439</v>
+        <v>2779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8789,10 +8785,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R66" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8839,17 +8835,17 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8867,10 +8863,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123313167</v>
+        <v>123313384</v>
       </c>
       <c r="B67" t="n">
-        <v>74775</v>
+        <v>80456</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8879,29 +8875,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -8910,10 +8914,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R67" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8960,17 +8964,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8988,10 +8992,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123313433</v>
+        <v>123313092</v>
       </c>
       <c r="B68" t="n">
-        <v>74775</v>
+        <v>80456</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9000,29 +9004,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1118</v>
+        <v>738</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -9031,10 +9043,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432147</v>
+        <v>432268</v>
       </c>
       <c r="R68" t="n">
-        <v>6152962</v>
+        <v>6152997</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9067,6 +9079,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9109,10 +9126,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123313362</v>
+        <v>123312986</v>
       </c>
       <c r="B69" t="n">
-        <v>74775</v>
+        <v>95206</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9121,30 +9138,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9152,10 +9170,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432240</v>
+        <v>432217</v>
       </c>
       <c r="R69" t="n">
-        <v>6153018</v>
+        <v>6152972</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9190,11 +9208,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9207,17 +9220,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9235,10 +9248,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123313436</v>
+        <v>123313163</v>
       </c>
       <c r="B70" t="n">
-        <v>95206</v>
+        <v>77124</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9247,31 +9260,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9279,10 +9291,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432147</v>
+        <v>432332</v>
       </c>
       <c r="R70" t="n">
-        <v>6152962</v>
+        <v>6152958</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9317,6 +9329,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal avenbok</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9329,17 +9346,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9357,10 +9374,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313000</v>
+        <v>123313107</v>
       </c>
       <c r="B71" t="n">
-        <v>95416</v>
+        <v>95412</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9373,21 +9390,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9401,10 +9418,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432217</v>
+        <v>432268</v>
       </c>
       <c r="R71" t="n">
-        <v>6152972</v>
+        <v>6152997</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9437,11 +9454,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9484,10 +9496,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313163</v>
+        <v>123313105</v>
       </c>
       <c r="B72" t="n">
-        <v>77124</v>
+        <v>95206</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9496,30 +9508,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9527,10 +9540,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432332</v>
+        <v>432268</v>
       </c>
       <c r="R72" t="n">
-        <v>6152958</v>
+        <v>6152997</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9565,11 +9578,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal avenbok</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9582,17 +9590,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9610,10 +9618,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123313109</v>
+        <v>123312991</v>
       </c>
       <c r="B73" t="n">
-        <v>95161</v>
+        <v>95412</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9626,21 +9634,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2676</v>
+        <v>2667</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9654,10 +9662,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R73" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9732,10 +9740,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123313092</v>
+        <v>123313425</v>
       </c>
       <c r="B74" t="n">
-        <v>80456</v>
+        <v>95412</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9744,38 +9752,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>738</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9783,10 +9784,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432268</v>
+        <v>432198</v>
       </c>
       <c r="R74" t="n">
-        <v>6152997</v>
+        <v>6152961</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9819,11 +9820,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Liten förekomst i dåligt skick.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9866,10 +9862,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123312991</v>
+        <v>123313422</v>
       </c>
       <c r="B75" t="n">
-        <v>95412</v>
+        <v>95206</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9882,21 +9878,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9910,10 +9906,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432217</v>
+        <v>432198</v>
       </c>
       <c r="R75" t="n">
-        <v>6152972</v>
+        <v>6152961</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10110,10 +10106,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123313420</v>
+        <v>123313208</v>
       </c>
       <c r="B77" t="n">
-        <v>74775</v>
+        <v>74780</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10122,25 +10118,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1118</v>
+        <v>1458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10153,10 +10149,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432198</v>
+        <v>432329</v>
       </c>
       <c r="R77" t="n">
-        <v>6152961</v>
+        <v>6152963</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10203,17 +10199,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10231,10 +10227,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123312983</v>
+        <v>123313433</v>
       </c>
       <c r="B78" t="n">
-        <v>80456</v>
+        <v>74775</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10243,25 +10239,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>738</v>
+        <v>1118</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10274,10 +10270,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432217</v>
+        <v>432147</v>
       </c>
       <c r="R78" t="n">
-        <v>6152972</v>
+        <v>6152962</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10310,11 +10306,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10357,10 +10348,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123313105</v>
+        <v>123313000</v>
       </c>
       <c r="B79" t="n">
-        <v>95206</v>
+        <v>95416</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10373,21 +10364,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2779</v>
+        <v>2668</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10401,10 +10392,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432268</v>
+        <v>432217</v>
       </c>
       <c r="R79" t="n">
-        <v>6152997</v>
+        <v>6152972</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10437,6 +10428,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10479,10 +10475,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123313155</v>
+        <v>123312983</v>
       </c>
       <c r="B80" t="n">
-        <v>109775</v>
+        <v>80456</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10491,35 +10487,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222776</v>
+        <v>738</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10527,10 +10518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432332</v>
+        <v>432217</v>
       </c>
       <c r="R80" t="n">
-        <v>6152958</v>
+        <v>6152972</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10565,6 +10556,11 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På samma lönn som Per Appeltofft noterat arten tidigare.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10574,6 +10570,21 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10590,10 +10601,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123312986</v>
+        <v>123313167</v>
       </c>
       <c r="B81" t="n">
-        <v>95206</v>
+        <v>74775</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10602,31 +10613,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2779</v>
+        <v>1118</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10634,10 +10644,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432217</v>
+        <v>432332</v>
       </c>
       <c r="R81" t="n">
-        <v>6152972</v>
+        <v>6152958</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10684,17 +10694,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>avenbok</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10712,10 +10722,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123313422</v>
+        <v>123313438</v>
       </c>
       <c r="B82" t="n">
-        <v>95206</v>
+        <v>74863</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10728,27 +10738,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2779</v>
+        <v>6439</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10756,10 +10765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R82" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10834,10 +10843,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123313384</v>
+        <v>123313446</v>
       </c>
       <c r="B83" t="n">
-        <v>80456</v>
+        <v>79168</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10846,37 +10855,29 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>738</v>
+        <v>6431</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
@@ -10885,10 +10886,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432198</v>
+        <v>432147</v>
       </c>
       <c r="R83" t="n">
-        <v>6152961</v>
+        <v>6152962</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10963,10 +10964,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123313165</v>
+        <v>123313420</v>
       </c>
       <c r="B84" t="n">
-        <v>95206</v>
+        <v>74775</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10975,31 +10976,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2779</v>
+        <v>1118</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>432332</v>
+        <v>432198</v>
       </c>
       <c r="R84" t="n">
-        <v>6152958</v>
+        <v>6152961</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11057,17 +11057,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>avenbok</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Carpinus betulus</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -9374,10 +9374,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123313107</v>
+        <v>123313105</v>
       </c>
       <c r="B71" t="n">
-        <v>95412</v>
+        <v>95206</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9390,21 +9390,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9496,10 +9496,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123313105</v>
+        <v>123313107</v>
       </c>
       <c r="B72" t="n">
-        <v>95206</v>
+        <v>95412</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9512,21 +9512,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11210,6 +11210,250 @@
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125870649</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8930</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100928</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Hålskenknäppare</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Eucnemis capucinus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ahrens, 1812</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Örups almskog, 250 m SV Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>432532</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6153002</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Sållning av insekts- (trol bl.a. Sinodendron och hästmyror) och svampangripna (mestadels vitrötade) ekstockar, samt något lös bark, inklusive en bok och en ask. ESILs Nationaldagsexkursion.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr"/>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125870652</v>
+      </c>
+      <c r="B87" t="n">
+        <v>7663</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>101549</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Bokvedvivel</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Phloeophagus lignarius</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Marsham, 1802)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Örups almskog, 250 m SV Örup, Sk</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>432532</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6153002</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Benestad</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Under lös bokbark. ESILs Nationaldagsexkursion.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr"/>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -11459,7 +11459,7 @@
         <v>126996066</v>
       </c>
       <c r="B88" t="n">
-        <v>12692</v>
+        <v>12695</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>126996032</v>
       </c>
       <c r="B89" t="n">
-        <v>12687</v>
+        <v>12690</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,12 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99802</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5969,10 +5964,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432386.4431641277</v>
+        <v>432386</v>
       </c>
       <c r="R44" t="n">
-        <v>6153090.629382072</v>
+        <v>6153091</v>
       </c>
       <c r="S44" t="n">
         <v>100</v>
@@ -6002,19 +5997,9 @@
           <t>1997-07-16</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>1997-07-16</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6063,12 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107479</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6100,10 +6080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432386.4431641277</v>
+        <v>432386</v>
       </c>
       <c r="R45" t="n">
-        <v>6153090.629382072</v>
+        <v>6153091</v>
       </c>
       <c r="S45" t="n">
         <v>100</v>
@@ -6133,19 +6113,9 @@
           <t>1997-07-16</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>1997-07-16</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6194,12 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110324</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6231,10 +6196,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432386.4431641277</v>
+        <v>432386</v>
       </c>
       <c r="R46" t="n">
-        <v>6153090.629382072</v>
+        <v>6153091</v>
       </c>
       <c r="S46" t="n">
         <v>100</v>
@@ -6264,19 +6229,9 @@
           <t>1997-07-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>1997-07-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6325,12 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109210</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6362,10 +6312,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432386.4431641277</v>
+        <v>432386</v>
       </c>
       <c r="R47" t="n">
-        <v>6153090.629382072</v>
+        <v>6153091</v>
       </c>
       <c r="S47" t="n">
         <v>100</v>
@@ -6395,19 +6345,9 @@
           <t>1997-07-16</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>1997-07-16</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6456,12 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>103602</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6493,10 +6428,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432386.4431641277</v>
+        <v>432386</v>
       </c>
       <c r="R48" t="n">
-        <v>6153090.629382072</v>
+        <v>6153091</v>
       </c>
       <c r="S48" t="n">
         <v>100</v>
@@ -6526,19 +6461,9 @@
           <t>1997-07-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>1997-07-16</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6587,12 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>96361</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98613</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6624,10 +6544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>432386.4431641277</v>
+        <v>432386</v>
       </c>
       <c r="R49" t="n">
-        <v>6153090.629382072</v>
+        <v>6153091</v>
       </c>
       <c r="S49" t="n">
         <v>100</v>
@@ -6657,19 +6577,9 @@
           <t>1998-04-27</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>1998-04-27</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99802</v>
+        <v>99805</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107479</v>
+        <v>107491</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110324</v>
+        <v>110337</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109210</v>
+        <v>109223</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>105977</v>
+        <v>105989</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98613</v>
+        <v>98616</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99805</v>
+        <v>99810</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107491</v>
+        <v>107500</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110337</v>
+        <v>110346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>105989</v>
+        <v>105998</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98616</v>
+        <v>98619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99810</v>
+        <v>99811</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107500</v>
+        <v>107505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110346</v>
+        <v>110351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>105998</v>
+        <v>106003</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98619</v>
+        <v>98620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99811</v>
+        <v>99838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110351</v>
+        <v>110379</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106003</v>
+        <v>106031</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98620</v>
+        <v>98647</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99838</v>
+        <v>99844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107533</v>
+        <v>107539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110379</v>
+        <v>110385</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109265</v>
+        <v>109271</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98647</v>
+        <v>98653</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99844</v>
+        <v>99851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107539</v>
+        <v>107546</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110385</v>
+        <v>110392</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109271</v>
+        <v>109278</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106037</v>
+        <v>106044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98653</v>
+        <v>98660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99851</v>
+        <v>99855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110392</v>
+        <v>110396</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106044</v>
+        <v>106048</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98660</v>
+        <v>98664</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99855</v>
+        <v>99862</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107550</v>
+        <v>107558</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110396</v>
+        <v>110404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106048</v>
+        <v>106055</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98664</v>
+        <v>98671</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99865</v>
+        <v>99870</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107561</v>
+        <v>107566</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110407</v>
+        <v>110412</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109293</v>
+        <v>109298</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106058</v>
+        <v>106063</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99870</v>
+        <v>99878</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107566</v>
+        <v>107574</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110412</v>
+        <v>110420</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109298</v>
+        <v>109306</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106063</v>
+        <v>106071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98679</v>
+        <v>98687</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -5932,7 +5932,7 @@
         <v>63121818</v>
       </c>
       <c r="B44" t="n">
-        <v>99878</v>
+        <v>99888</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>63121827</v>
       </c>
       <c r="B45" t="n">
-        <v>107574</v>
+        <v>107584</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>63121817</v>
       </c>
       <c r="B46" t="n">
-        <v>110420</v>
+        <v>110430</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>63121828</v>
       </c>
       <c r="B47" t="n">
-        <v>109306</v>
+        <v>109316</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106071</v>
+        <v>106081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>63122362</v>
       </c>
       <c r="B49" t="n">
-        <v>98687</v>
+        <v>98697</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100778</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>126996066</v>
       </c>
       <c r="B88" t="n">
-        <v>12695</v>
+        <v>12692</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>126996032</v>
       </c>
       <c r="B89" t="n">
-        <v>12690</v>
+        <v>12687</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -11354,7 +11354,7 @@
         <v>126996066</v>
       </c>
       <c r="B88" t="n">
-        <v>12692</v>
+        <v>12695</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>126996032</v>
       </c>
       <c r="B89" t="n">
-        <v>12687</v>
+        <v>12690</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100867</v>
+        <v>100870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -1058,7 +1058,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100870</v>
+        <v>100896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>103601</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432390.6772521053</v>
+        <v>432391</v>
       </c>
       <c r="R2" t="n">
-        <v>6152886.773687283</v>
+        <v>6152887</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,19 +748,9 @@
           <t>2009-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,12 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>105081</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6381,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106081</v>
+        <v>106366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7557,12 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>103602</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106366</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7599,10 +7574,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432378.6704156185</v>
+        <v>432379</v>
       </c>
       <c r="R57" t="n">
-        <v>6152880.731607789</v>
+        <v>6152881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7632,19 +7607,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7684,12 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>104120</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100896</v>
+        <v>100897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingrid Andersson, Lennart Bengtsson</t>
+          <t>Lennart Bengtsson, Ingrid Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100897</v>
+        <v>100898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lennart Bengtsson, Ingrid Andersson</t>
+          <t>Ingrid Andersson, Lennart Bengtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100898</v>
+        <v>100900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>5473389</v>
       </c>
       <c r="B5" t="n">
-        <v>100900</v>
+        <v>100904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377827</v>
       </c>
       <c r="B2" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>377298</v>
       </c>
       <c r="B3" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>63121823</v>
       </c>
       <c r="B48" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>101475553</v>
       </c>
       <c r="B57" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>111942881</v>
       </c>
       <c r="B58" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 29860-2022 artfynd.xlsx
+++ b/artfynd/A 29860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/274390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63121818</t>
         </is>
       </c>
     </row>
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116865233</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122879089</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123312983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313092</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313384</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1610,6 +1650,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370076</t>
         </is>
       </c>
     </row>
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313167</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1849,6 +1899,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313362</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1965,6 +2020,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313420</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2081,6 +2141,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313433</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2188,6 +2253,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632523</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632801</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2402,6 +2477,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132633528</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2513,6 +2593,11 @@
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370075</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2625,6 +2710,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/377827</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2741,6 +2831,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63121823</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2852,6 +2947,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102651018</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2964,6 +3064,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101475553</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3074,6 +3179,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942881</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3178,6 +3288,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370074</t>
         </is>
       </c>
     </row>
@@ -3301,6 +3416,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313163</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3410,6 +3530,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t>Skyddsvärda lavar i sydvästra Sverige</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86370073</t>
         </is>
       </c>
     </row>
@@ -3528,6 +3653,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313208</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3645,6 +3775,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123312991</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3762,6 +3897,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313107</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3879,6 +4019,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313425</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3986,6 +4131,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632420</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4108,6 +4258,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313000</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4225,6 +4380,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313426</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4347,6 +4507,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632499</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4469,6 +4634,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123312996</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4586,6 +4756,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313109</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4693,6 +4868,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632396</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4810,6 +4990,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123312986</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4927,6 +5112,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313105</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5044,6 +5234,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313165</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5161,6 +5356,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313365</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5278,6 +5478,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313422</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5395,6 +5600,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313436</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5511,6 +5721,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313446</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5622,6 +5837,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632536</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5738,6 +5958,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313438</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5859,6 +6084,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126996032</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5994,6 +6224,11 @@
           <t>PheroBio-projektet. Feromoninventering av Biodiversitet</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74684112</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6129,6 +6364,11 @@
           <t>PheroBio-projektet. Feromoninventering av Biodiversitet</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74684119</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6264,6 +6504,11 @@
           <t>PheroBio-projektet. Feromoninventering av Biodiversitet</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74684124</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6386,6 +6631,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870649</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6508,6 +6758,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870652</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6615,6 +6870,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126996066</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6731,6 +6991,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63122362</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6847,6 +7112,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63121827</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6963,6 +7233,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63121828</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7073,6 +7348,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83451858</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7183,6 +7463,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83455825</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7293,6 +7578,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83455826</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7403,6 +7693,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83456896</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7513,6 +7808,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83457722</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7623,6 +7923,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83459350</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7733,6 +8038,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83470409</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7843,6 +8153,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83472564</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7953,6 +8268,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83482740</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8063,6 +8383,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83486193</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8173,6 +8498,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83487497</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8283,6 +8613,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83487498</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8393,6 +8728,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83490749</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8503,6 +8843,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83490750</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8613,6 +8958,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83490755</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8723,6 +9073,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83490756</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8833,6 +9188,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83490757</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8943,6 +9303,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83501185</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9053,6 +9418,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83501186</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9163,6 +9533,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83501867</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9278,6 +9653,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83501870</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9388,6 +9768,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83501878</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9498,6 +9883,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83502458</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9614,6 +10004,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63121817</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9720,6 +10115,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123313155</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9836,6 +10236,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5460733</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9943,6 +10348,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132632777</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10065,6 +10475,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132633014</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10192,8 +10607,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132633275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>